--- a/data_lake/macro/Europe/Employment.xlsx
+++ b/data_lake/macro/Europe/Employment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Europe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8C305C-26A0-4401-AEA9-010B9E536320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9474952E-D846-425A-BDFF-EF60C33F7900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{484F5785-4531-4BC2-998A-8344EB3D0817}"/>
+    <workbookView minimized="1" xWindow="912" yWindow="1812" windowWidth="21600" windowHeight="10872" activeTab="1" xr2:uid="{484F5785-4531-4BC2-998A-8344EB3D0817}"/>
   </bookViews>
   <sheets>
     <sheet name="EURUEMEM" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://kr.investing.com/economic-calendar/unemployment-rate-299</t>
-  </si>
-  <si>
     <t>Source</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -86,17 +83,21 @@
     <t>No</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>https://kr.investing.com/economic-calendar/unemployment-rate-299</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="180" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="182" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +131,14 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -170,15 +179,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -188,22 +200,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -218,10 +230,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="백분율" xfId="1" builtinId="5"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -576,7 +592,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D2" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="D2:D65" si="0">IF(
  AND(
   B2 &gt;= EOMONTH(DATE(YEAR(B2),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B2),3,1),0),1)
@@ -608,20 +624,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D3" s="9" t="str">
-        <f>IF(
- AND(
-  B3 &gt;= EOMONTH(DATE(YEAR(B3),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B3),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B3 &lt; EOMONTH(DATE(YEAR(B3),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B3),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E3" s="1">
@@ -642,20 +645,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D4" s="9" t="str">
-        <f>IF(
- AND(
-  B4 &gt;= EOMONTH(DATE(YEAR(B4),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B4),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B4 &lt; EOMONTH(DATE(YEAR(B4),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B4),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E4" s="1">
@@ -676,20 +666,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D5" s="9" t="str">
-        <f>IF(
- AND(
-  B5 &gt;= EOMONTH(DATE(YEAR(B5),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B5),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B5 &lt; EOMONTH(DATE(YEAR(B5),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B5),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E5" s="1">
@@ -710,20 +687,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D6" s="9" t="str">
-        <f>IF(
- AND(
-  B6 &gt;= EOMONTH(DATE(YEAR(B6),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B6),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B6 &lt; EOMONTH(DATE(YEAR(B6),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B6),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E6" s="1">
@@ -744,20 +708,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D7" s="9" t="str">
-        <f>IF(
- AND(
-  B7 &gt;= EOMONTH(DATE(YEAR(B7),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B7),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B7 &lt; EOMONTH(DATE(YEAR(B7),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B7),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E7" s="1">
@@ -778,20 +729,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D8" s="9" t="str">
-        <f>IF(
- AND(
-  B8 &gt;= EOMONTH(DATE(YEAR(B8),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B8),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B8 &lt; EOMONTH(DATE(YEAR(B8),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B8),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E8" s="1">
@@ -812,20 +750,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D9" s="9" t="str">
-        <f>IF(
- AND(
-  B9 &gt;= EOMONTH(DATE(YEAR(B9),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B9),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B9 &lt; EOMONTH(DATE(YEAR(B9),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B9),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E9" s="1">
@@ -846,20 +771,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D10" s="9" t="str">
-        <f>IF(
- AND(
-  B10 &gt;= EOMONTH(DATE(YEAR(B10),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B10),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B10 &lt; EOMONTH(DATE(YEAR(B10),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B10),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E10" s="1">
@@ -880,20 +792,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D11" s="9" t="str">
-        <f>IF(
- AND(
-  B11 &gt;= EOMONTH(DATE(YEAR(B11),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B11),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B11 &lt; EOMONTH(DATE(YEAR(B11),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B11),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E11" s="1">
@@ -914,20 +813,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D12" s="9" t="str">
-        <f>IF(
- AND(
-  B12 &gt;= EOMONTH(DATE(YEAR(B12),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B12),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B12 &lt; EOMONTH(DATE(YEAR(B12),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B12),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E12" s="1">
@@ -948,20 +834,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D13" s="9" t="str">
-        <f>IF(
- AND(
-  B13 &gt;= EOMONTH(DATE(YEAR(B13),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B13),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B13 &lt; EOMONTH(DATE(YEAR(B13),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B13),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E13" s="1">
@@ -982,20 +855,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D14" s="9" t="str">
-        <f>IF(
- AND(
-  B14 &gt;= EOMONTH(DATE(YEAR(B14),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B14),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B14 &lt; EOMONTH(DATE(YEAR(B14),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B14),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E14" s="1">
@@ -1016,20 +876,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D15" s="9" t="str">
-        <f>IF(
- AND(
-  B15 &gt;= EOMONTH(DATE(YEAR(B15),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B15),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B15 &lt; EOMONTH(DATE(YEAR(B15),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B15),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E15" s="1">
@@ -1050,20 +897,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="9" t="str">
-        <f>IF(
- AND(
-  B16 &gt;= EOMONTH(DATE(YEAR(B16),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B16),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B16 &lt; EOMONTH(DATE(YEAR(B16),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B16),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E16" s="1">
@@ -1084,20 +918,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D17" s="9" t="str">
-        <f>IF(
- AND(
-  B17 &gt;= EOMONTH(DATE(YEAR(B17),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B17),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B17 &lt; EOMONTH(DATE(YEAR(B17),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B17),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E17" s="1">
@@ -1118,20 +939,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D18" s="9" t="str">
-        <f>IF(
- AND(
-  B18 &gt;= EOMONTH(DATE(YEAR(B18),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B18),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B18 &lt; EOMONTH(DATE(YEAR(B18),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B18),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E18" s="1">
@@ -1152,20 +960,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D19" s="9" t="str">
-        <f>IF(
- AND(
-  B19 &gt;= EOMONTH(DATE(YEAR(B19),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B19),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B19 &lt; EOMONTH(DATE(YEAR(B19),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B19),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E19" s="1">
@@ -1186,20 +981,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D20" s="9" t="str">
-        <f>IF(
- AND(
-  B20 &gt;= EOMONTH(DATE(YEAR(B20),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B20),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B20 &lt; EOMONTH(DATE(YEAR(B20),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B20),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E20" s="1">
@@ -1220,20 +1002,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D21" s="9" t="str">
-        <f>IF(
- AND(
-  B21 &gt;= EOMONTH(DATE(YEAR(B21),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B21),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B21 &lt; EOMONTH(DATE(YEAR(B21),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B21),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E21" s="1">
@@ -1254,20 +1023,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D22" s="9" t="str">
-        <f>IF(
- AND(
-  B22 &gt;= EOMONTH(DATE(YEAR(B22),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B22),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B22 &lt; EOMONTH(DATE(YEAR(B22),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B22),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E22" s="1">
@@ -1288,20 +1044,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D23" s="9" t="str">
-        <f>IF(
- AND(
-  B23 &gt;= EOMONTH(DATE(YEAR(B23),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B23),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B23 &lt; EOMONTH(DATE(YEAR(B23),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B23),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E23" s="1">
@@ -1322,20 +1065,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D24" s="9" t="str">
-        <f>IF(
- AND(
-  B24 &gt;= EOMONTH(DATE(YEAR(B24),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B24),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B24 &lt; EOMONTH(DATE(YEAR(B24),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B24),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E24" s="1">
@@ -1356,20 +1086,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D25" s="9" t="str">
-        <f>IF(
- AND(
-  B25 &gt;= EOMONTH(DATE(YEAR(B25),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B25),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B25 &lt; EOMONTH(DATE(YEAR(B25),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B25),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E25" s="1">
@@ -1390,20 +1107,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D26" s="9" t="str">
-        <f>IF(
- AND(
-  B26 &gt;= EOMONTH(DATE(YEAR(B26),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B26),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B26 &lt; EOMONTH(DATE(YEAR(B26),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B26),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E26" s="1">
@@ -1424,20 +1128,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D27" s="9" t="str">
-        <f>IF(
- AND(
-  B27 &gt;= EOMONTH(DATE(YEAR(B27),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B27),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B27 &lt; EOMONTH(DATE(YEAR(B27),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B27),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E27" s="1">
@@ -1458,20 +1149,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="9" t="str">
-        <f>IF(
- AND(
-  B28 &gt;= EOMONTH(DATE(YEAR(B28),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B28),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B28 &lt; EOMONTH(DATE(YEAR(B28),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B28),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E28" s="1">
@@ -1492,20 +1170,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D29" s="9" t="str">
-        <f>IF(
- AND(
-  B29 &gt;= EOMONTH(DATE(YEAR(B29),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B29),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B29 &lt; EOMONTH(DATE(YEAR(B29),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B29),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E29" s="1">
@@ -1526,20 +1191,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D30" s="9" t="str">
-        <f>IF(
- AND(
-  B30 &gt;= EOMONTH(DATE(YEAR(B30),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B30),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B30 &lt; EOMONTH(DATE(YEAR(B30),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B30),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E30" s="1">
@@ -1560,20 +1212,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D31" s="9" t="str">
-        <f>IF(
- AND(
-  B31 &gt;= EOMONTH(DATE(YEAR(B31),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B31),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B31 &lt; EOMONTH(DATE(YEAR(B31),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B31),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E31" s="1">
@@ -1594,20 +1233,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D32" s="9" t="str">
-        <f>IF(
- AND(
-  B32 &gt;= EOMONTH(DATE(YEAR(B32),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B32),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B32 &lt; EOMONTH(DATE(YEAR(B32),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B32),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E32" s="1">
@@ -1628,20 +1254,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D33" s="9" t="str">
-        <f>IF(
- AND(
-  B33 &gt;= EOMONTH(DATE(YEAR(B33),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B33),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B33 &lt; EOMONTH(DATE(YEAR(B33),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B33),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E33" s="1">
@@ -1662,20 +1275,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D34" s="9" t="str">
-        <f>IF(
- AND(
-  B34 &gt;= EOMONTH(DATE(YEAR(B34),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B34),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B34 &lt; EOMONTH(DATE(YEAR(B34),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B34),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E34" s="1">
@@ -1696,20 +1296,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D35" s="9" t="str">
-        <f>IF(
- AND(
-  B35 &gt;= EOMONTH(DATE(YEAR(B35),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B35),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B35 &lt; EOMONTH(DATE(YEAR(B35),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B35),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E35" s="1">
@@ -1730,20 +1317,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D36" s="9" t="str">
-        <f>IF(
- AND(
-  B36 &gt;= EOMONTH(DATE(YEAR(B36),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B36),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B36 &lt; EOMONTH(DATE(YEAR(B36),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B36),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E36" s="1">
@@ -1764,20 +1338,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D37" s="9" t="str">
-        <f>IF(
- AND(
-  B37 &gt;= EOMONTH(DATE(YEAR(B37),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B37),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B37 &lt; EOMONTH(DATE(YEAR(B37),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B37),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E37" s="1">
@@ -1798,20 +1359,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D38" s="9" t="str">
-        <f>IF(
- AND(
-  B38 &gt;= EOMONTH(DATE(YEAR(B38),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B38),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B38 &lt; EOMONTH(DATE(YEAR(B38),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B38),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E38" s="1">
@@ -1832,20 +1380,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D39" s="9" t="str">
-        <f>IF(
- AND(
-  B39 &gt;= EOMONTH(DATE(YEAR(B39),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B39),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B39 &lt; EOMONTH(DATE(YEAR(B39),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B39),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E39" s="1">
@@ -1866,20 +1401,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D40" s="9" t="str">
-        <f>IF(
- AND(
-  B40 &gt;= EOMONTH(DATE(YEAR(B40),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B40),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B40 &lt; EOMONTH(DATE(YEAR(B40),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B40),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E40" s="1">
@@ -1900,20 +1422,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D41" s="9" t="str">
-        <f>IF(
- AND(
-  B41 &gt;= EOMONTH(DATE(YEAR(B41),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B41),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B41 &lt; EOMONTH(DATE(YEAR(B41),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B41),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E41" s="1">
@@ -1934,20 +1443,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D42" s="9" t="str">
-        <f>IF(
- AND(
-  B42 &gt;= EOMONTH(DATE(YEAR(B42),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B42),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B42 &lt; EOMONTH(DATE(YEAR(B42),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B42),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E42" s="1">
@@ -1968,20 +1464,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D43" s="9" t="str">
-        <f>IF(
- AND(
-  B43 &gt;= EOMONTH(DATE(YEAR(B43),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B43),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B43 &lt; EOMONTH(DATE(YEAR(B43),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B43),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E43" s="1">
@@ -2002,20 +1485,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D44" s="9" t="str">
-        <f>IF(
- AND(
-  B44 &gt;= EOMONTH(DATE(YEAR(B44),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B44),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B44 &lt; EOMONTH(DATE(YEAR(B44),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B44),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E44" s="1">
@@ -2036,20 +1506,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D45" s="9" t="str">
-        <f>IF(
- AND(
-  B45 &gt;= EOMONTH(DATE(YEAR(B45),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B45),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B45 &lt; EOMONTH(DATE(YEAR(B45),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B45),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E45" s="1">
@@ -2070,20 +1527,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D46" s="9" t="str">
-        <f>IF(
- AND(
-  B46 &gt;= EOMONTH(DATE(YEAR(B46),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B46),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B46 &lt; EOMONTH(DATE(YEAR(B46),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B46),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E46" s="1">
@@ -2104,20 +1548,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D47" s="9" t="str">
-        <f>IF(
- AND(
-  B47 &gt;= EOMONTH(DATE(YEAR(B47),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B47),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B47 &lt; EOMONTH(DATE(YEAR(B47),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B47),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E47" s="1">
@@ -2138,20 +1569,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D48" s="9" t="str">
-        <f>IF(
- AND(
-  B48 &gt;= EOMONTH(DATE(YEAR(B48),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B48),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B48 &lt; EOMONTH(DATE(YEAR(B48),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B48),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E48" s="1">
@@ -2172,20 +1590,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D49" s="9" t="str">
-        <f>IF(
- AND(
-  B49 &gt;= EOMONTH(DATE(YEAR(B49),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B49),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B49 &lt; EOMONTH(DATE(YEAR(B49),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B49),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E49" s="1">
@@ -2206,20 +1611,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D50" s="9" t="str">
-        <f>IF(
- AND(
-  B50 &gt;= EOMONTH(DATE(YEAR(B50),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B50),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B50 &lt; EOMONTH(DATE(YEAR(B50),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B50),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E50" s="1">
@@ -2240,20 +1632,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D51" s="9" t="str">
-        <f>IF(
- AND(
-  B51 &gt;= EOMONTH(DATE(YEAR(B51),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B51),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B51 &lt; EOMONTH(DATE(YEAR(B51),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B51),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E51" s="1">
@@ -2274,20 +1653,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D52" s="9" t="str">
-        <f>IF(
- AND(
-  B52 &gt;= EOMONTH(DATE(YEAR(B52),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B52),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B52 &lt; EOMONTH(DATE(YEAR(B52),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B52),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E52" s="1">
@@ -2308,20 +1674,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D53" s="9" t="str">
-        <f>IF(
- AND(
-  B53 &gt;= EOMONTH(DATE(YEAR(B53),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B53),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B53 &lt; EOMONTH(DATE(YEAR(B53),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B53),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E53" s="1">
@@ -2342,20 +1695,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D54" s="9" t="str">
-        <f>IF(
- AND(
-  B54 &gt;= EOMONTH(DATE(YEAR(B54),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B54),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B54 &lt; EOMONTH(DATE(YEAR(B54),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B54),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E54" s="1">
@@ -2376,20 +1716,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D55" s="9" t="str">
-        <f>IF(
- AND(
-  B55 &gt;= EOMONTH(DATE(YEAR(B55),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B55),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B55 &lt; EOMONTH(DATE(YEAR(B55),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B55),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E55" s="1">
@@ -2410,20 +1737,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D56" s="9" t="str">
-        <f>IF(
- AND(
-  B56 &gt;= EOMONTH(DATE(YEAR(B56),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B56),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B56 &lt; EOMONTH(DATE(YEAR(B56),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B56),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E56" s="1">
@@ -2444,20 +1758,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D57" s="9" t="str">
-        <f>IF(
- AND(
-  B57 &gt;= EOMONTH(DATE(YEAR(B57),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B57),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B57 &lt; EOMONTH(DATE(YEAR(B57),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B57),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E57" s="1">
@@ -2478,20 +1779,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D58" s="9" t="str">
-        <f>IF(
- AND(
-  B58 &gt;= EOMONTH(DATE(YEAR(B58),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B58),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B58 &lt; EOMONTH(DATE(YEAR(B58),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B58),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E58" s="1">
@@ -2512,20 +1800,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D59" s="9" t="str">
-        <f>IF(
- AND(
-  B59 &gt;= EOMONTH(DATE(YEAR(B59),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B59),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B59 &lt; EOMONTH(DATE(YEAR(B59),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B59),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E59" s="1">
@@ -2546,20 +1821,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D60" s="9" t="str">
-        <f>IF(
- AND(
-  B60 &gt;= EOMONTH(DATE(YEAR(B60),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B60),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B60 &lt; EOMONTH(DATE(YEAR(B60),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B60),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
       <c r="E60" s="1">
@@ -2580,20 +1842,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D61" s="9" t="str">
-        <f>IF(
- AND(
-  B61 &gt;= EOMONTH(DATE(YEAR(B61),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B61),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B61 &lt; EOMONTH(DATE(YEAR(B61),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B61),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E61" s="1">
@@ -2614,20 +1863,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D62" s="9" t="str">
-        <f>IF(
- AND(
-  B62 &gt;= EOMONTH(DATE(YEAR(B62),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B62),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B62 &lt; EOMONTH(DATE(YEAR(B62),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B62),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E62" s="1">
@@ -2648,20 +1884,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D63" s="9" t="str">
-        <f>IF(
- AND(
-  B63 &gt;= EOMONTH(DATE(YEAR(B63),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B63),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B63 &lt; EOMONTH(DATE(YEAR(B63),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B63),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E63" s="1">
@@ -2682,20 +1905,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D64" s="9" t="str">
-        <f>IF(
- AND(
-  B64 &gt;= EOMONTH(DATE(YEAR(B64),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B64),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B64 &lt; EOMONTH(DATE(YEAR(B64),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B64),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E64" s="1">
@@ -2716,20 +1926,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D65" s="9" t="str">
-        <f>IF(
- AND(
-  B65 &gt;= EOMONTH(DATE(YEAR(B65),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B65),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B65 &lt; EOMONTH(DATE(YEAR(B65),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B65),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
       <c r="E65" s="1">
@@ -2750,7 +1947,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D66" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="D66:D129" si="1">IF(
  AND(
   B66 &gt;= EOMONTH(DATE(YEAR(B66),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B66),3,1),0),1)
@@ -2784,20 +1981,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D67" s="9" t="str">
-        <f>IF(
- AND(
-  B67 &gt;= EOMONTH(DATE(YEAR(B67),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B67),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B67 &lt; EOMONTH(DATE(YEAR(B67),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B67),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E67" s="1">
@@ -2818,20 +2002,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D68" s="9" t="str">
-        <f>IF(
- AND(
-  B68 &gt;= EOMONTH(DATE(YEAR(B68),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B68),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B68 &lt; EOMONTH(DATE(YEAR(B68),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B68),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E68" s="1">
@@ -2852,20 +2023,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D69" s="9" t="str">
-        <f>IF(
- AND(
-  B69 &gt;= EOMONTH(DATE(YEAR(B69),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B69),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B69 &lt; EOMONTH(DATE(YEAR(B69),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B69),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E69" s="1">
@@ -2886,20 +2044,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D70" s="9" t="str">
-        <f>IF(
- AND(
-  B70 &gt;= EOMONTH(DATE(YEAR(B70),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B70),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B70 &lt; EOMONTH(DATE(YEAR(B70),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B70),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E70" s="1">
@@ -2920,20 +2065,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D71" s="9" t="str">
-        <f>IF(
- AND(
-  B71 &gt;= EOMONTH(DATE(YEAR(B71),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B71),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B71 &lt; EOMONTH(DATE(YEAR(B71),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B71),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E71" s="1">
@@ -2954,20 +2086,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D72" s="9" t="str">
-        <f>IF(
- AND(
-  B72 &gt;= EOMONTH(DATE(YEAR(B72),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B72),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B72 &lt; EOMONTH(DATE(YEAR(B72),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B72),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E72" s="1">
@@ -2988,20 +2107,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D73" s="9" t="str">
-        <f>IF(
- AND(
-  B73 &gt;= EOMONTH(DATE(YEAR(B73),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B73),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B73 &lt; EOMONTH(DATE(YEAR(B73),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B73),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E73" s="1">
@@ -3022,20 +2128,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D74" s="9" t="str">
-        <f>IF(
- AND(
-  B74 &gt;= EOMONTH(DATE(YEAR(B74),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B74),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B74 &lt; EOMONTH(DATE(YEAR(B74),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B74),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E74" s="1">
@@ -3056,20 +2149,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D75" s="9" t="str">
-        <f>IF(
- AND(
-  B75 &gt;= EOMONTH(DATE(YEAR(B75),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B75),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B75 &lt; EOMONTH(DATE(YEAR(B75),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B75),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E75" s="1">
@@ -3090,20 +2170,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D76" s="9" t="str">
-        <f>IF(
- AND(
-  B76 &gt;= EOMONTH(DATE(YEAR(B76),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B76),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B76 &lt; EOMONTH(DATE(YEAR(B76),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B76),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E76" s="1">
@@ -3124,20 +2191,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D77" s="9" t="str">
-        <f>IF(
- AND(
-  B77 &gt;= EOMONTH(DATE(YEAR(B77),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B77),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B77 &lt; EOMONTH(DATE(YEAR(B77),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B77),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E77" s="1">
@@ -3158,20 +2212,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D78" s="9" t="str">
-        <f>IF(
- AND(
-  B78 &gt;= EOMONTH(DATE(YEAR(B78),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B78),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B78 &lt; EOMONTH(DATE(YEAR(B78),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B78),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E78" s="1">
@@ -3192,20 +2233,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D79" s="9" t="str">
-        <f>IF(
- AND(
-  B79 &gt;= EOMONTH(DATE(YEAR(B79),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B79),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B79 &lt; EOMONTH(DATE(YEAR(B79),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B79),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E79" s="1">
@@ -3226,20 +2254,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D80" s="9" t="str">
-        <f>IF(
- AND(
-  B80 &gt;= EOMONTH(DATE(YEAR(B80),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B80),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B80 &lt; EOMONTH(DATE(YEAR(B80),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B80),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E80" s="1">
@@ -3260,20 +2275,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D81" s="9" t="str">
-        <f>IF(
- AND(
-  B81 &gt;= EOMONTH(DATE(YEAR(B81),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B81),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B81 &lt; EOMONTH(DATE(YEAR(B81),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B81),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E81" s="1">
@@ -3294,20 +2296,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D82" s="9" t="str">
-        <f>IF(
- AND(
-  B82 &gt;= EOMONTH(DATE(YEAR(B82),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B82),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B82 &lt; EOMONTH(DATE(YEAR(B82),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B82),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E82" s="1">
@@ -3328,20 +2317,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D83" s="9" t="str">
-        <f>IF(
- AND(
-  B83 &gt;= EOMONTH(DATE(YEAR(B83),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B83),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B83 &lt; EOMONTH(DATE(YEAR(B83),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B83),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E83" s="1">
@@ -3362,20 +2338,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D84" s="9" t="str">
-        <f>IF(
- AND(
-  B84 &gt;= EOMONTH(DATE(YEAR(B84),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B84),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B84 &lt; EOMONTH(DATE(YEAR(B84),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B84),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E84" s="1">
@@ -3396,20 +2359,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D85" s="9" t="str">
-        <f>IF(
- AND(
-  B85 &gt;= EOMONTH(DATE(YEAR(B85),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B85),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B85 &lt; EOMONTH(DATE(YEAR(B85),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B85),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E85" s="1">
@@ -3430,20 +2380,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D86" s="9" t="str">
-        <f>IF(
- AND(
-  B86 &gt;= EOMONTH(DATE(YEAR(B86),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B86),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B86 &lt; EOMONTH(DATE(YEAR(B86),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B86),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E86" s="1">
@@ -3464,20 +2401,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D87" s="9" t="str">
-        <f>IF(
- AND(
-  B87 &gt;= EOMONTH(DATE(YEAR(B87),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B87),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B87 &lt; EOMONTH(DATE(YEAR(B87),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B87),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E87" s="1">
@@ -3498,20 +2422,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D88" s="9" t="str">
-        <f>IF(
- AND(
-  B88 &gt;= EOMONTH(DATE(YEAR(B88),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B88),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B88 &lt; EOMONTH(DATE(YEAR(B88),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B88),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E88" s="1">
@@ -3532,20 +2443,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D89" s="9" t="str">
-        <f>IF(
- AND(
-  B89 &gt;= EOMONTH(DATE(YEAR(B89),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B89),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B89 &lt; EOMONTH(DATE(YEAR(B89),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B89),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E89" s="1">
@@ -3566,20 +2464,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D90" s="9" t="str">
-        <f>IF(
- AND(
-  B90 &gt;= EOMONTH(DATE(YEAR(B90),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B90),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B90 &lt; EOMONTH(DATE(YEAR(B90),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B90),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E90" s="1">
@@ -3600,20 +2485,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D91" s="9" t="str">
-        <f>IF(
- AND(
-  B91 &gt;= EOMONTH(DATE(YEAR(B91),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B91),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B91 &lt; EOMONTH(DATE(YEAR(B91),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B91),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E91" s="1">
@@ -3634,20 +2506,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D92" s="9" t="str">
-        <f>IF(
- AND(
-  B92 &gt;= EOMONTH(DATE(YEAR(B92),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B92),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B92 &lt; EOMONTH(DATE(YEAR(B92),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B92),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E92" s="1">
@@ -3668,20 +2527,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D93" s="9" t="str">
-        <f>IF(
- AND(
-  B93 &gt;= EOMONTH(DATE(YEAR(B93),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B93),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B93 &lt; EOMONTH(DATE(YEAR(B93),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B93),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E93" s="1">
@@ -3702,20 +2548,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D94" s="9" t="str">
-        <f>IF(
- AND(
-  B94 &gt;= EOMONTH(DATE(YEAR(B94),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B94),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B94 &lt; EOMONTH(DATE(YEAR(B94),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B94),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E94" s="1">
@@ -3736,20 +2569,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D95" s="9" t="str">
-        <f>IF(
- AND(
-  B95 &gt;= EOMONTH(DATE(YEAR(B95),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B95),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B95 &lt; EOMONTH(DATE(YEAR(B95),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B95),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E95" s="1">
@@ -3770,20 +2590,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D96" s="9" t="str">
-        <f>IF(
- AND(
-  B96 &gt;= EOMONTH(DATE(YEAR(B96),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B96),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B96 &lt; EOMONTH(DATE(YEAR(B96),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B96),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E96" s="1">
@@ -3804,20 +2611,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D97" s="9" t="str">
-        <f>IF(
- AND(
-  B97 &gt;= EOMONTH(DATE(YEAR(B97),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B97),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B97 &lt; EOMONTH(DATE(YEAR(B97),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B97),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E97" s="1">
@@ -3838,20 +2632,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D98" s="9" t="str">
-        <f>IF(
- AND(
-  B98 &gt;= EOMONTH(DATE(YEAR(B98),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B98),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B98 &lt; EOMONTH(DATE(YEAR(B98),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B98),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E98" s="1">
@@ -3872,20 +2653,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D99" s="9" t="str">
-        <f>IF(
- AND(
-  B99 &gt;= EOMONTH(DATE(YEAR(B99),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B99),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B99 &lt; EOMONTH(DATE(YEAR(B99),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B99),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E99" s="1">
@@ -3906,20 +2674,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D100" s="9" t="str">
-        <f>IF(
- AND(
-  B100 &gt;= EOMONTH(DATE(YEAR(B100),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B100),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B100 &lt; EOMONTH(DATE(YEAR(B100),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B100),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E100" s="1">
@@ -3940,20 +2695,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D101" s="9" t="str">
-        <f>IF(
- AND(
-  B101 &gt;= EOMONTH(DATE(YEAR(B101),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B101),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B101 &lt; EOMONTH(DATE(YEAR(B101),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B101),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E101" s="1">
@@ -3974,20 +2716,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D102" s="9" t="str">
-        <f>IF(
- AND(
-  B102 &gt;= EOMONTH(DATE(YEAR(B102),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B102),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B102 &lt; EOMONTH(DATE(YEAR(B102),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B102),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E102" s="1">
@@ -4008,20 +2737,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D103" s="9" t="str">
-        <f>IF(
- AND(
-  B103 &gt;= EOMONTH(DATE(YEAR(B103),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B103),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B103 &lt; EOMONTH(DATE(YEAR(B103),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B103),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E103" s="1">
@@ -4042,20 +2758,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D104" s="9" t="str">
-        <f>IF(
- AND(
-  B104 &gt;= EOMONTH(DATE(YEAR(B104),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B104),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B104 &lt; EOMONTH(DATE(YEAR(B104),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B104),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E104" s="1">
@@ -4076,20 +2779,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D105" s="9" t="str">
-        <f>IF(
- AND(
-  B105 &gt;= EOMONTH(DATE(YEAR(B105),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B105),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B105 &lt; EOMONTH(DATE(YEAR(B105),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B105),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E105" s="1">
@@ -4110,20 +2800,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D106" s="9" t="str">
-        <f>IF(
- AND(
-  B106 &gt;= EOMONTH(DATE(YEAR(B106),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B106),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B106 &lt; EOMONTH(DATE(YEAR(B106),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B106),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E106" s="1">
@@ -4144,20 +2821,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D107" s="9" t="str">
-        <f>IF(
- AND(
-  B107 &gt;= EOMONTH(DATE(YEAR(B107),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B107),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B107 &lt; EOMONTH(DATE(YEAR(B107),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B107),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E107" s="1">
@@ -4178,20 +2842,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D108" s="9" t="str">
-        <f>IF(
- AND(
-  B108 &gt;= EOMONTH(DATE(YEAR(B108),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B108),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B108 &lt; EOMONTH(DATE(YEAR(B108),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B108),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E108" s="1">
@@ -4212,20 +2863,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D109" s="9" t="str">
-        <f>IF(
- AND(
-  B109 &gt;= EOMONTH(DATE(YEAR(B109),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B109),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B109 &lt; EOMONTH(DATE(YEAR(B109),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B109),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E109" s="1">
@@ -4246,20 +2884,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D110" s="9" t="str">
-        <f>IF(
- AND(
-  B110 &gt;= EOMONTH(DATE(YEAR(B110),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B110),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B110 &lt; EOMONTH(DATE(YEAR(B110),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B110),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E110" s="1">
@@ -4280,20 +2905,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D111" s="9" t="str">
-        <f>IF(
- AND(
-  B111 &gt;= EOMONTH(DATE(YEAR(B111),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B111),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B111 &lt; EOMONTH(DATE(YEAR(B111),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B111),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E111" s="1">
@@ -4314,20 +2926,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D112" s="9" t="str">
-        <f>IF(
- AND(
-  B112 &gt;= EOMONTH(DATE(YEAR(B112),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B112),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B112 &lt; EOMONTH(DATE(YEAR(B112),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B112),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E112" s="1">
@@ -4348,20 +2947,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D113" s="9" t="str">
-        <f>IF(
- AND(
-  B113 &gt;= EOMONTH(DATE(YEAR(B113),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B113),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B113 &lt; EOMONTH(DATE(YEAR(B113),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B113),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E113" s="1">
@@ -4382,20 +2968,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D114" s="9" t="str">
-        <f>IF(
- AND(
-  B114 &gt;= EOMONTH(DATE(YEAR(B114),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B114),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B114 &lt; EOMONTH(DATE(YEAR(B114),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B114),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E114" s="1">
@@ -4416,20 +2989,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D115" s="9" t="str">
-        <f>IF(
- AND(
-  B115 &gt;= EOMONTH(DATE(YEAR(B115),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B115),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B115 &lt; EOMONTH(DATE(YEAR(B115),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B115),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E115" s="1">
@@ -4450,20 +3010,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D116" s="9" t="str">
-        <f>IF(
- AND(
-  B116 &gt;= EOMONTH(DATE(YEAR(B116),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B116),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B116 &lt; EOMONTH(DATE(YEAR(B116),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B116),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E116" s="1">
@@ -4484,20 +3031,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D117" s="9" t="str">
-        <f>IF(
- AND(
-  B117 &gt;= EOMONTH(DATE(YEAR(B117),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B117),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B117 &lt; EOMONTH(DATE(YEAR(B117),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B117),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E117" s="1">
@@ -4518,20 +3052,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D118" s="9" t="str">
-        <f>IF(
- AND(
-  B118 &gt;= EOMONTH(DATE(YEAR(B118),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B118),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B118 &lt; EOMONTH(DATE(YEAR(B118),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B118),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E118" s="1">
@@ -4552,20 +3073,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D119" s="9" t="str">
-        <f>IF(
- AND(
-  B119 &gt;= EOMONTH(DATE(YEAR(B119),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B119),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B119 &lt; EOMONTH(DATE(YEAR(B119),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B119),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E119" s="1">
@@ -4586,20 +3094,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D120" s="9" t="str">
-        <f>IF(
- AND(
-  B120 &gt;= EOMONTH(DATE(YEAR(B120),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B120),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B120 &lt; EOMONTH(DATE(YEAR(B120),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B120),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E120" s="1">
@@ -4620,20 +3115,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D121" s="9" t="str">
-        <f>IF(
- AND(
-  B121 &gt;= EOMONTH(DATE(YEAR(B121),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B121),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B121 &lt; EOMONTH(DATE(YEAR(B121),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B121),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E121" s="1">
@@ -4657,20 +3139,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D122" s="9" t="str">
-        <f>IF(
- AND(
-  B122 &gt;= EOMONTH(DATE(YEAR(B122),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B122),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B122 &lt; EOMONTH(DATE(YEAR(B122),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B122),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E122" s="1">
@@ -4694,20 +3163,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D123" s="9" t="str">
-        <f>IF(
- AND(
-  B123 &gt;= EOMONTH(DATE(YEAR(B123),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B123),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B123 &lt; EOMONTH(DATE(YEAR(B123),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B123),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E123" s="1">
@@ -4731,20 +3187,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D124" s="9" t="str">
-        <f>IF(
- AND(
-  B124 &gt;= EOMONTH(DATE(YEAR(B124),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B124),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B124 &lt; EOMONTH(DATE(YEAR(B124),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B124),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E124" s="1">
@@ -4768,20 +3211,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D125" s="9" t="str">
-        <f>IF(
- AND(
-  B125 &gt;= EOMONTH(DATE(YEAR(B125),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B125),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B125 &lt; EOMONTH(DATE(YEAR(B125),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B125),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E125" s="1">
@@ -4805,20 +3235,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D126" s="9" t="str">
-        <f>IF(
- AND(
-  B126 &gt;= EOMONTH(DATE(YEAR(B126),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B126),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B126 &lt; EOMONTH(DATE(YEAR(B126),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B126),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
       <c r="E126" s="1">
@@ -4842,20 +3259,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D127" s="9" t="str">
-        <f>IF(
- AND(
-  B127 &gt;= EOMONTH(DATE(YEAR(B127),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B127),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B127 &lt; EOMONTH(DATE(YEAR(B127),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B127),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E127" s="1">
@@ -4879,20 +3283,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D128" s="9" t="str">
-        <f>IF(
- AND(
-  B128 &gt;= EOMONTH(DATE(YEAR(B128),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B128),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B128 &lt; EOMONTH(DATE(YEAR(B128),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B128),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E128" s="1">
@@ -4916,20 +3307,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D129" s="9" t="str">
-        <f>IF(
- AND(
-  B129 &gt;= EOMONTH(DATE(YEAR(B129),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B129),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B129 &lt; EOMONTH(DATE(YEAR(B129),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B129),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
       <c r="E129" s="1">
@@ -4953,7 +3331,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D130" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="D130:D193" si="2">IF(
  AND(
   B130 &gt;= EOMONTH(DATE(YEAR(B130),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B130),3,1),0),1)
@@ -4990,20 +3368,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D131" s="9" t="str">
-        <f>IF(
- AND(
-  B131 &gt;= EOMONTH(DATE(YEAR(B131),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B131),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B131 &lt; EOMONTH(DATE(YEAR(B131),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B131),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E131" s="1">
@@ -5027,20 +3392,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D132" s="9" t="str">
-        <f>IF(
- AND(
-  B132 &gt;= EOMONTH(DATE(YEAR(B132),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B132),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B132 &lt; EOMONTH(DATE(YEAR(B132),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B132),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E132" s="1">
@@ -5064,20 +3416,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D133" s="9" t="str">
-        <f>IF(
- AND(
-  B133 &gt;= EOMONTH(DATE(YEAR(B133),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B133),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B133 &lt; EOMONTH(DATE(YEAR(B133),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B133),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E133" s="1">
@@ -5101,20 +3440,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D134" s="9" t="str">
-        <f>IF(
- AND(
-  B134 &gt;= EOMONTH(DATE(YEAR(B134),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B134),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B134 &lt; EOMONTH(DATE(YEAR(B134),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B134),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E134" s="1">
@@ -5138,20 +3464,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D135" s="9" t="str">
-        <f>IF(
- AND(
-  B135 &gt;= EOMONTH(DATE(YEAR(B135),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B135),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B135 &lt; EOMONTH(DATE(YEAR(B135),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B135),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E135" s="1">
@@ -5175,20 +3488,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D136" s="9" t="str">
-        <f>IF(
- AND(
-  B136 &gt;= EOMONTH(DATE(YEAR(B136),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B136),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B136 &lt; EOMONTH(DATE(YEAR(B136),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B136),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E136" s="1">
@@ -5212,20 +3512,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D137" s="9" t="str">
-        <f>IF(
- AND(
-  B137 &gt;= EOMONTH(DATE(YEAR(B137),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B137),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B137 &lt; EOMONTH(DATE(YEAR(B137),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B137),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E137" s="1">
@@ -5249,20 +3536,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D138" s="9" t="str">
-        <f>IF(
- AND(
-  B138 &gt;= EOMONTH(DATE(YEAR(B138),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B138),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B138 &lt; EOMONTH(DATE(YEAR(B138),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B138),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E138" s="1">
@@ -5286,20 +3560,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D139" s="9" t="str">
-        <f>IF(
- AND(
-  B139 &gt;= EOMONTH(DATE(YEAR(B139),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B139),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B139 &lt; EOMONTH(DATE(YEAR(B139),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B139),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E139" s="1">
@@ -5323,20 +3584,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D140" s="9" t="str">
-        <f>IF(
- AND(
-  B140 &gt;= EOMONTH(DATE(YEAR(B140),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B140),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B140 &lt; EOMONTH(DATE(YEAR(B140),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B140),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E140" s="1">
@@ -5360,20 +3608,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D141" s="9" t="str">
-        <f>IF(
- AND(
-  B141 &gt;= EOMONTH(DATE(YEAR(B141),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B141),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B141 &lt; EOMONTH(DATE(YEAR(B141),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B141),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E141" s="1">
@@ -5397,20 +3632,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D142" s="9" t="str">
-        <f>IF(
- AND(
-  B142 &gt;= EOMONTH(DATE(YEAR(B142),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B142),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B142 &lt; EOMONTH(DATE(YEAR(B142),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B142),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E142" s="1">
@@ -5434,20 +3656,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D143" s="9" t="str">
-        <f>IF(
- AND(
-  B143 &gt;= EOMONTH(DATE(YEAR(B143),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B143),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B143 &lt; EOMONTH(DATE(YEAR(B143),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B143),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E143" s="1">
@@ -5471,20 +3680,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D144" s="9" t="str">
-        <f>IF(
- AND(
-  B144 &gt;= EOMONTH(DATE(YEAR(B144),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B144),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B144 &lt; EOMONTH(DATE(YEAR(B144),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B144),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E144" s="1">
@@ -5508,20 +3704,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D145" s="9" t="str">
-        <f>IF(
- AND(
-  B145 &gt;= EOMONTH(DATE(YEAR(B145),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B145),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B145 &lt; EOMONTH(DATE(YEAR(B145),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B145),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E145" s="1">
@@ -5545,20 +3728,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D146" s="9" t="str">
-        <f>IF(
- AND(
-  B146 &gt;= EOMONTH(DATE(YEAR(B146),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B146),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B146 &lt; EOMONTH(DATE(YEAR(B146),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B146),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E146" s="1">
@@ -5582,20 +3752,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D147" s="9" t="str">
-        <f>IF(
- AND(
-  B147 &gt;= EOMONTH(DATE(YEAR(B147),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B147),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B147 &lt; EOMONTH(DATE(YEAR(B147),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B147),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E147" s="1">
@@ -5619,20 +3776,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D148" s="9" t="str">
-        <f>IF(
- AND(
-  B148 &gt;= EOMONTH(DATE(YEAR(B148),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B148),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B148 &lt; EOMONTH(DATE(YEAR(B148),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B148),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E148" s="1">
@@ -5656,20 +3800,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D149" s="9" t="str">
-        <f>IF(
- AND(
-  B149 &gt;= EOMONTH(DATE(YEAR(B149),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B149),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B149 &lt; EOMONTH(DATE(YEAR(B149),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B149),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E149" s="1">
@@ -5693,20 +3824,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D150" s="9" t="str">
-        <f>IF(
- AND(
-  B150 &gt;= EOMONTH(DATE(YEAR(B150),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B150),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B150 &lt; EOMONTH(DATE(YEAR(B150),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B150),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E150" s="1">
@@ -5730,20 +3848,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D151" s="9" t="str">
-        <f>IF(
- AND(
-  B151 &gt;= EOMONTH(DATE(YEAR(B151),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B151),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B151 &lt; EOMONTH(DATE(YEAR(B151),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B151),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E151" s="1">
@@ -5767,20 +3872,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D152" s="9" t="str">
-        <f>IF(
- AND(
-  B152 &gt;= EOMONTH(DATE(YEAR(B152),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B152),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B152 &lt; EOMONTH(DATE(YEAR(B152),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B152),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E152" s="1">
@@ -5804,20 +3896,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D153" s="9" t="str">
-        <f>IF(
- AND(
-  B153 &gt;= EOMONTH(DATE(YEAR(B153),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B153),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B153 &lt; EOMONTH(DATE(YEAR(B153),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B153),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E153" s="1">
@@ -5841,20 +3920,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D154" s="9" t="str">
-        <f>IF(
- AND(
-  B154 &gt;= EOMONTH(DATE(YEAR(B154),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B154),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B154 &lt; EOMONTH(DATE(YEAR(B154),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B154),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E154" s="1">
@@ -5878,20 +3944,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D155" s="9" t="str">
-        <f>IF(
- AND(
-  B155 &gt;= EOMONTH(DATE(YEAR(B155),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B155),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B155 &lt; EOMONTH(DATE(YEAR(B155),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B155),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E155" s="1">
@@ -5915,20 +3968,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D156" s="9" t="str">
-        <f>IF(
- AND(
-  B156 &gt;= EOMONTH(DATE(YEAR(B156),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B156),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B156 &lt; EOMONTH(DATE(YEAR(B156),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B156),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E156" s="1">
@@ -5952,20 +3992,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D157" s="9" t="str">
-        <f>IF(
- AND(
-  B157 &gt;= EOMONTH(DATE(YEAR(B157),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B157),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B157 &lt; EOMONTH(DATE(YEAR(B157),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B157),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E157" s="1">
@@ -5989,20 +4016,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D158" s="9" t="str">
-        <f>IF(
- AND(
-  B158 &gt;= EOMONTH(DATE(YEAR(B158),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B158),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B158 &lt; EOMONTH(DATE(YEAR(B158),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B158),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E158" s="1">
@@ -6026,20 +4040,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D159" s="9" t="str">
-        <f>IF(
- AND(
-  B159 &gt;= EOMONTH(DATE(YEAR(B159),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B159),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B159 &lt; EOMONTH(DATE(YEAR(B159),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B159),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E159" s="1">
@@ -6063,20 +4064,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D160" s="9" t="str">
-        <f>IF(
- AND(
-  B160 &gt;= EOMONTH(DATE(YEAR(B160),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B160),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B160 &lt; EOMONTH(DATE(YEAR(B160),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B160),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E160" s="1">
@@ -6100,20 +4088,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D161" s="9" t="str">
-        <f>IF(
- AND(
-  B161 &gt;= EOMONTH(DATE(YEAR(B161),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B161),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B161 &lt; EOMONTH(DATE(YEAR(B161),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B161),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E161" s="1">
@@ -6137,20 +4112,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D162" s="9" t="str">
-        <f>IF(
- AND(
-  B162 &gt;= EOMONTH(DATE(YEAR(B162),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B162),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B162 &lt; EOMONTH(DATE(YEAR(B162),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B162),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E162" s="1">
@@ -6174,20 +4136,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D163" s="9" t="str">
-        <f>IF(
- AND(
-  B163 &gt;= EOMONTH(DATE(YEAR(B163),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B163),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B163 &lt; EOMONTH(DATE(YEAR(B163),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B163),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E163" s="1">
@@ -6211,20 +4160,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D164" s="9" t="str">
-        <f>IF(
- AND(
-  B164 &gt;= EOMONTH(DATE(YEAR(B164),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B164),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B164 &lt; EOMONTH(DATE(YEAR(B164),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B164),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E164" s="1">
@@ -6248,20 +4184,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D165" s="9" t="str">
-        <f>IF(
- AND(
-  B165 &gt;= EOMONTH(DATE(YEAR(B165),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B165),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B165 &lt; EOMONTH(DATE(YEAR(B165),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B165),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E165" s="1">
@@ -6285,20 +4208,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D166" s="9" t="str">
-        <f>IF(
- AND(
-  B166 &gt;= EOMONTH(DATE(YEAR(B166),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B166),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B166 &lt; EOMONTH(DATE(YEAR(B166),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B166),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E166" s="1">
@@ -6322,20 +4232,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D167" s="9" t="str">
-        <f>IF(
- AND(
-  B167 &gt;= EOMONTH(DATE(YEAR(B167),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B167),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B167 &lt; EOMONTH(DATE(YEAR(B167),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B167),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E167" s="1">
@@ -6359,20 +4256,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D168" s="9" t="str">
-        <f>IF(
- AND(
-  B168 &gt;= EOMONTH(DATE(YEAR(B168),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B168),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B168 &lt; EOMONTH(DATE(YEAR(B168),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B168),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E168" s="1">
@@ -6396,20 +4280,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D169" s="9" t="str">
-        <f>IF(
- AND(
-  B169 &gt;= EOMONTH(DATE(YEAR(B169),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B169),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B169 &lt; EOMONTH(DATE(YEAR(B169),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B169),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E169" s="1">
@@ -6433,20 +4304,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D170" s="9" t="str">
-        <f>IF(
- AND(
-  B170 &gt;= EOMONTH(DATE(YEAR(B170),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B170),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B170 &lt; EOMONTH(DATE(YEAR(B170),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B170),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E170" s="1">
@@ -6470,20 +4328,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D171" s="9" t="str">
-        <f>IF(
- AND(
-  B171 &gt;= EOMONTH(DATE(YEAR(B171),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B171),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B171 &lt; EOMONTH(DATE(YEAR(B171),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B171),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E171" s="1">
@@ -6507,20 +4352,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D172" s="9" t="str">
-        <f>IF(
- AND(
-  B172 &gt;= EOMONTH(DATE(YEAR(B172),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B172),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B172 &lt; EOMONTH(DATE(YEAR(B172),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B172),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E172" s="1">
@@ -6544,20 +4376,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D173" s="9" t="str">
-        <f>IF(
- AND(
-  B173 &gt;= EOMONTH(DATE(YEAR(B173),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B173),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B173 &lt; EOMONTH(DATE(YEAR(B173),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B173),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E173" s="1">
@@ -6581,20 +4400,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D174" s="9" t="str">
-        <f>IF(
- AND(
-  B174 &gt;= EOMONTH(DATE(YEAR(B174),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B174),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B174 &lt; EOMONTH(DATE(YEAR(B174),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B174),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E174" s="1">
@@ -6618,20 +4424,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D175" s="9" t="str">
-        <f>IF(
- AND(
-  B175 &gt;= EOMONTH(DATE(YEAR(B175),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B175),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B175 &lt; EOMONTH(DATE(YEAR(B175),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B175),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E175" s="1">
@@ -6655,20 +4448,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D176" s="9" t="str">
-        <f>IF(
- AND(
-  B176 &gt;= EOMONTH(DATE(YEAR(B176),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B176),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B176 &lt; EOMONTH(DATE(YEAR(B176),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B176),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E176" s="1">
@@ -6692,20 +4472,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D177" s="9" t="str">
-        <f>IF(
- AND(
-  B177 &gt;= EOMONTH(DATE(YEAR(B177),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B177),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B177 &lt; EOMONTH(DATE(YEAR(B177),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B177),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E177" s="1">
@@ -6729,20 +4496,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D178" s="9" t="str">
-        <f>IF(
- AND(
-  B178 &gt;= EOMONTH(DATE(YEAR(B178),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B178),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B178 &lt; EOMONTH(DATE(YEAR(B178),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B178),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E178" s="1">
@@ -6766,20 +4520,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D179" s="9" t="str">
-        <f>IF(
- AND(
-  B179 &gt;= EOMONTH(DATE(YEAR(B179),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B179),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B179 &lt; EOMONTH(DATE(YEAR(B179),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B179),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E179" s="1">
@@ -6803,20 +4544,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D180" s="9" t="str">
-        <f>IF(
- AND(
-  B180 &gt;= EOMONTH(DATE(YEAR(B180),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B180),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B180 &lt; EOMONTH(DATE(YEAR(B180),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B180),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E180" s="1">
@@ -6840,20 +4568,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D181" s="9" t="str">
-        <f>IF(
- AND(
-  B181 &gt;= EOMONTH(DATE(YEAR(B181),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B181),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B181 &lt; EOMONTH(DATE(YEAR(B181),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B181),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E181" s="1">
@@ -6877,20 +4592,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D182" s="9" t="str">
-        <f>IF(
- AND(
-  B182 &gt;= EOMONTH(DATE(YEAR(B182),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B182),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B182 &lt; EOMONTH(DATE(YEAR(B182),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B182),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E182" s="1">
@@ -6914,20 +4616,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D183" s="9" t="str">
-        <f>IF(
- AND(
-  B183 &gt;= EOMONTH(DATE(YEAR(B183),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B183),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B183 &lt; EOMONTH(DATE(YEAR(B183),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B183),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E183" s="1">
@@ -6951,20 +4640,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D184" s="9" t="str">
-        <f>IF(
- AND(
-  B184 &gt;= EOMONTH(DATE(YEAR(B184),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B184),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B184 &lt; EOMONTH(DATE(YEAR(B184),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B184),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E184" s="1">
@@ -6988,20 +4664,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D185" s="9" t="str">
-        <f>IF(
- AND(
-  B185 &gt;= EOMONTH(DATE(YEAR(B185),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B185),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B185 &lt; EOMONTH(DATE(YEAR(B185),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B185),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E185" s="1">
@@ -7025,20 +4688,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D186" s="9" t="str">
-        <f>IF(
- AND(
-  B186 &gt;= EOMONTH(DATE(YEAR(B186),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B186),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B186 &lt; EOMONTH(DATE(YEAR(B186),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B186),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E186" s="1">
@@ -7062,20 +4712,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D187" s="9" t="str">
-        <f>IF(
- AND(
-  B187 &gt;= EOMONTH(DATE(YEAR(B187),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B187),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B187 &lt; EOMONTH(DATE(YEAR(B187),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B187),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E187" s="1">
@@ -7099,20 +4736,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D188" s="9" t="str">
-        <f>IF(
- AND(
-  B188 &gt;= EOMONTH(DATE(YEAR(B188),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B188),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B188 &lt; EOMONTH(DATE(YEAR(B188),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B188),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E188" s="1">
@@ -7136,20 +4760,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D189" s="9" t="str">
-        <f>IF(
- AND(
-  B189 &gt;= EOMONTH(DATE(YEAR(B189),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B189),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B189 &lt; EOMONTH(DATE(YEAR(B189),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B189),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E189" s="1">
@@ -7173,20 +4784,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D190" s="9" t="str">
-        <f>IF(
- AND(
-  B190 &gt;= EOMONTH(DATE(YEAR(B190),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B190),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B190 &lt; EOMONTH(DATE(YEAR(B190),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B190),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E190" s="1">
@@ -7210,20 +4808,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D191" s="9" t="str">
-        <f>IF(
- AND(
-  B191 &gt;= EOMONTH(DATE(YEAR(B191),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B191),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B191 &lt; EOMONTH(DATE(YEAR(B191),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B191),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
       <c r="E191" s="1">
@@ -7247,20 +4832,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D192" s="9" t="str">
-        <f>IF(
- AND(
-  B192 &gt;= EOMONTH(DATE(YEAR(B192),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B192),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B192 &lt; EOMONTH(DATE(YEAR(B192),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B192),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E192" s="1">
@@ -7284,20 +4856,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D193" s="9" t="str">
-        <f>IF(
- AND(
-  B193 &gt;= EOMONTH(DATE(YEAR(B193),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B193),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B193 &lt; EOMONTH(DATE(YEAR(B193),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B193),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
       <c r="E193" s="1">
@@ -7321,7 +4880,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D194" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="D194:D257" si="3">IF(
  AND(
   B194 &gt;= EOMONTH(DATE(YEAR(B194),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B194),3,1),0),1)
@@ -7358,20 +4917,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D195" s="9" t="str">
-        <f>IF(
- AND(
-  B195 &gt;= EOMONTH(DATE(YEAR(B195),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B195),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B195 &lt; EOMONTH(DATE(YEAR(B195),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B195),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E195" s="1">
@@ -7395,20 +4941,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D196" s="9" t="str">
-        <f>IF(
- AND(
-  B196 &gt;= EOMONTH(DATE(YEAR(B196),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B196),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B196 &lt; EOMONTH(DATE(YEAR(B196),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B196),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E196" s="1">
@@ -7432,20 +4965,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D197" s="9" t="str">
-        <f>IF(
- AND(
-  B197 &gt;= EOMONTH(DATE(YEAR(B197),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B197),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B197 &lt; EOMONTH(DATE(YEAR(B197),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B197),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E197" s="1">
@@ -7469,20 +4989,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D198" s="9" t="str">
-        <f>IF(
- AND(
-  B198 &gt;= EOMONTH(DATE(YEAR(B198),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B198),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B198 &lt; EOMONTH(DATE(YEAR(B198),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B198),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E198" s="1">
@@ -7506,20 +5013,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D199" s="9" t="str">
-        <f>IF(
- AND(
-  B199 &gt;= EOMONTH(DATE(YEAR(B199),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B199),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B199 &lt; EOMONTH(DATE(YEAR(B199),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B199),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E199" s="1">
@@ -7543,20 +5037,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D200" s="9" t="str">
-        <f>IF(
- AND(
-  B200 &gt;= EOMONTH(DATE(YEAR(B200),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B200),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B200 &lt; EOMONTH(DATE(YEAR(B200),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B200),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E200" s="1">
@@ -7580,20 +5061,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D201" s="9" t="str">
-        <f>IF(
- AND(
-  B201 &gt;= EOMONTH(DATE(YEAR(B201),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B201),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B201 &lt; EOMONTH(DATE(YEAR(B201),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B201),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E201" s="1">
@@ -7617,20 +5085,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D202" s="9" t="str">
-        <f>IF(
- AND(
-  B202 &gt;= EOMONTH(DATE(YEAR(B202),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B202),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B202 &lt; EOMONTH(DATE(YEAR(B202),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B202),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E202" s="1">
@@ -7654,20 +5109,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D203" s="9" t="str">
-        <f>IF(
- AND(
-  B203 &gt;= EOMONTH(DATE(YEAR(B203),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B203),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B203 &lt; EOMONTH(DATE(YEAR(B203),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B203),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E203" s="1">
@@ -7691,20 +5133,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D204" s="9" t="str">
-        <f>IF(
- AND(
-  B204 &gt;= EOMONTH(DATE(YEAR(B204),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B204),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B204 &lt; EOMONTH(DATE(YEAR(B204),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B204),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E204" s="1">
@@ -7728,20 +5157,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D205" s="9" t="str">
-        <f>IF(
- AND(
-  B205 &gt;= EOMONTH(DATE(YEAR(B205),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B205),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B205 &lt; EOMONTH(DATE(YEAR(B205),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B205),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E205" s="1">
@@ -7765,20 +5181,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D206" s="9" t="str">
-        <f>IF(
- AND(
-  B206 &gt;= EOMONTH(DATE(YEAR(B206),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B206),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B206 &lt; EOMONTH(DATE(YEAR(B206),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B206),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E206" s="1">
@@ -7802,20 +5205,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D207" s="9" t="str">
-        <f>IF(
- AND(
-  B207 &gt;= EOMONTH(DATE(YEAR(B207),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B207),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B207 &lt; EOMONTH(DATE(YEAR(B207),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B207),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E207" s="1">
@@ -7839,20 +5229,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D208" s="9" t="str">
-        <f>IF(
- AND(
-  B208 &gt;= EOMONTH(DATE(YEAR(B208),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B208),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B208 &lt; EOMONTH(DATE(YEAR(B208),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B208),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E208" s="1">
@@ -7876,20 +5253,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D209" s="9" t="str">
-        <f>IF(
- AND(
-  B209 &gt;= EOMONTH(DATE(YEAR(B209),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B209),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B209 &lt; EOMONTH(DATE(YEAR(B209),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B209),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E209" s="1">
@@ -7913,20 +5277,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D210" s="9" t="str">
-        <f>IF(
- AND(
-  B210 &gt;= EOMONTH(DATE(YEAR(B210),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B210),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B210 &lt; EOMONTH(DATE(YEAR(B210),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B210),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E210" s="1">
@@ -7950,20 +5301,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D211" s="9" t="str">
-        <f>IF(
- AND(
-  B211 &gt;= EOMONTH(DATE(YEAR(B211),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B211),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B211 &lt; EOMONTH(DATE(YEAR(B211),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B211),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E211" s="1">
@@ -7987,20 +5325,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D212" s="9" t="str">
-        <f>IF(
- AND(
-  B212 &gt;= EOMONTH(DATE(YEAR(B212),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B212),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B212 &lt; EOMONTH(DATE(YEAR(B212),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B212),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E212" s="1">
@@ -8024,20 +5349,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D213" s="9" t="str">
-        <f>IF(
- AND(
-  B213 &gt;= EOMONTH(DATE(YEAR(B213),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B213),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B213 &lt; EOMONTH(DATE(YEAR(B213),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B213),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E213" s="1">
@@ -8061,20 +5373,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D214" s="9" t="str">
-        <f>IF(
- AND(
-  B214 &gt;= EOMONTH(DATE(YEAR(B214),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B214),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B214 &lt; EOMONTH(DATE(YEAR(B214),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B214),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E214" s="1">
@@ -8098,20 +5397,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D215" s="9" t="str">
-        <f>IF(
- AND(
-  B215 &gt;= EOMONTH(DATE(YEAR(B215),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B215),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B215 &lt; EOMONTH(DATE(YEAR(B215),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B215),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E215" s="1">
@@ -8135,20 +5421,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D216" s="9" t="str">
-        <f>IF(
- AND(
-  B216 &gt;= EOMONTH(DATE(YEAR(B216),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B216),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B216 &lt; EOMONTH(DATE(YEAR(B216),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B216),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E216" s="1">
@@ -8172,20 +5445,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D217" s="9" t="str">
-        <f>IF(
- AND(
-  B217 &gt;= EOMONTH(DATE(YEAR(B217),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B217),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B217 &lt; EOMONTH(DATE(YEAR(B217),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B217),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E217" s="1">
@@ -8209,20 +5469,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D218" s="9" t="str">
-        <f>IF(
- AND(
-  B218 &gt;= EOMONTH(DATE(YEAR(B218),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B218),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B218 &lt; EOMONTH(DATE(YEAR(B218),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B218),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E218" s="1">
@@ -8246,20 +5493,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D219" s="9" t="str">
-        <f>IF(
- AND(
-  B219 &gt;= EOMONTH(DATE(YEAR(B219),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B219),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B219 &lt; EOMONTH(DATE(YEAR(B219),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B219),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E219" s="1">
@@ -8283,20 +5517,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D220" s="9" t="str">
-        <f>IF(
- AND(
-  B220 &gt;= EOMONTH(DATE(YEAR(B220),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B220),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B220 &lt; EOMONTH(DATE(YEAR(B220),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B220),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E220" s="1">
@@ -8320,20 +5541,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D221" s="9" t="str">
-        <f>IF(
- AND(
-  B221 &gt;= EOMONTH(DATE(YEAR(B221),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B221),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B221 &lt; EOMONTH(DATE(YEAR(B221),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B221),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E221" s="1">
@@ -8357,20 +5565,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D222" s="9" t="str">
-        <f>IF(
- AND(
-  B222 &gt;= EOMONTH(DATE(YEAR(B222),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B222),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B222 &lt; EOMONTH(DATE(YEAR(B222),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B222),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E222" s="1">
@@ -8394,20 +5589,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D223" s="9" t="str">
-        <f>IF(
- AND(
-  B223 &gt;= EOMONTH(DATE(YEAR(B223),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B223),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B223 &lt; EOMONTH(DATE(YEAR(B223),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B223),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E223" s="1">
@@ -8431,20 +5613,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D224" s="9" t="str">
-        <f>IF(
- AND(
-  B224 &gt;= EOMONTH(DATE(YEAR(B224),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B224),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B224 &lt; EOMONTH(DATE(YEAR(B224),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B224),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E224" s="1">
@@ -8468,20 +5637,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D225" s="9" t="str">
-        <f>IF(
- AND(
-  B225 &gt;= EOMONTH(DATE(YEAR(B225),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B225),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B225 &lt; EOMONTH(DATE(YEAR(B225),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B225),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E225" s="1">
@@ -8505,20 +5661,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D226" s="9" t="str">
-        <f>IF(
- AND(
-  B226 &gt;= EOMONTH(DATE(YEAR(B226),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B226),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B226 &lt; EOMONTH(DATE(YEAR(B226),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B226),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E226" s="1">
@@ -8542,20 +5685,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D227" s="9" t="str">
-        <f>IF(
- AND(
-  B227 &gt;= EOMONTH(DATE(YEAR(B227),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B227),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B227 &lt; EOMONTH(DATE(YEAR(B227),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B227),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E227" s="1">
@@ -8579,20 +5709,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D228" s="9" t="str">
-        <f>IF(
- AND(
-  B228 &gt;= EOMONTH(DATE(YEAR(B228),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B228),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B228 &lt; EOMONTH(DATE(YEAR(B228),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B228),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E228" s="1">
@@ -8616,20 +5733,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D229" s="9" t="str">
-        <f>IF(
- AND(
-  B229 &gt;= EOMONTH(DATE(YEAR(B229),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B229),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B229 &lt; EOMONTH(DATE(YEAR(B229),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B229),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E229" s="1">
@@ -8653,20 +5757,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D230" s="9" t="str">
-        <f>IF(
- AND(
-  B230 &gt;= EOMONTH(DATE(YEAR(B230),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B230),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B230 &lt; EOMONTH(DATE(YEAR(B230),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B230),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E230" s="1">
@@ -8690,20 +5781,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D231" s="9" t="str">
-        <f>IF(
- AND(
-  B231 &gt;= EOMONTH(DATE(YEAR(B231),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B231),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B231 &lt; EOMONTH(DATE(YEAR(B231),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B231),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E231" s="1">
@@ -8727,20 +5805,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D232" s="9" t="str">
-        <f>IF(
- AND(
-  B232 &gt;= EOMONTH(DATE(YEAR(B232),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B232),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B232 &lt; EOMONTH(DATE(YEAR(B232),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B232),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E232" s="1">
@@ -8764,20 +5829,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D233" s="9" t="str">
-        <f>IF(
- AND(
-  B233 &gt;= EOMONTH(DATE(YEAR(B233),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B233),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B233 &lt; EOMONTH(DATE(YEAR(B233),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B233),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E233" s="1">
@@ -8801,20 +5853,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D234" s="9" t="str">
-        <f>IF(
- AND(
-  B234 &gt;= EOMONTH(DATE(YEAR(B234),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B234),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B234 &lt; EOMONTH(DATE(YEAR(B234),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B234),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E234" s="1">
@@ -8838,20 +5877,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D235" s="9" t="str">
-        <f>IF(
- AND(
-  B235 &gt;= EOMONTH(DATE(YEAR(B235),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B235),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B235 &lt; EOMONTH(DATE(YEAR(B235),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B235),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E235" s="1">
@@ -8875,20 +5901,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D236" s="9" t="str">
-        <f>IF(
- AND(
-  B236 &gt;= EOMONTH(DATE(YEAR(B236),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B236),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B236 &lt; EOMONTH(DATE(YEAR(B236),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B236),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E236" s="1">
@@ -8912,20 +5925,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D237" s="9" t="str">
-        <f>IF(
- AND(
-  B237 &gt;= EOMONTH(DATE(YEAR(B237),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B237),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B237 &lt; EOMONTH(DATE(YEAR(B237),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B237),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E237" s="1">
@@ -8949,20 +5949,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D238" s="9" t="str">
-        <f>IF(
- AND(
-  B238 &gt;= EOMONTH(DATE(YEAR(B238),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B238),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B238 &lt; EOMONTH(DATE(YEAR(B238),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B238),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E238" s="1">
@@ -8986,20 +5973,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D239" s="9" t="str">
-        <f>IF(
- AND(
-  B239 &gt;= EOMONTH(DATE(YEAR(B239),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B239),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B239 &lt; EOMONTH(DATE(YEAR(B239),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B239),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E239" s="1">
@@ -9023,20 +5997,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D240" s="9" t="str">
-        <f>IF(
- AND(
-  B240 &gt;= EOMONTH(DATE(YEAR(B240),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B240),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B240 &lt; EOMONTH(DATE(YEAR(B240),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B240),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E240" s="1">
@@ -9060,20 +6021,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D241" s="9" t="str">
-        <f>IF(
- AND(
-  B241 &gt;= EOMONTH(DATE(YEAR(B241),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B241),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B241 &lt; EOMONTH(DATE(YEAR(B241),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B241),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E241" s="1">
@@ -9097,20 +6045,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D242" s="9" t="str">
-        <f>IF(
- AND(
-  B242 &gt;= EOMONTH(DATE(YEAR(B242),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B242),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B242 &lt; EOMONTH(DATE(YEAR(B242),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B242),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E242" s="1">
@@ -9134,20 +6069,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D243" s="9" t="str">
-        <f>IF(
- AND(
-  B243 &gt;= EOMONTH(DATE(YEAR(B243),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B243),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B243 &lt; EOMONTH(DATE(YEAR(B243),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B243),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E243" s="1">
@@ -9171,20 +6093,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D244" s="9" t="str">
-        <f>IF(
- AND(
-  B244 &gt;= EOMONTH(DATE(YEAR(B244),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B244),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B244 &lt; EOMONTH(DATE(YEAR(B244),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B244),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E244" s="1">
@@ -9208,20 +6117,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D245" s="9" t="str">
-        <f>IF(
- AND(
-  B245 &gt;= EOMONTH(DATE(YEAR(B245),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B245),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B245 &lt; EOMONTH(DATE(YEAR(B245),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B245),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E245" s="1">
@@ -9245,20 +6141,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D246" s="9" t="str">
-        <f>IF(
- AND(
-  B246 &gt;= EOMONTH(DATE(YEAR(B246),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B246),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B246 &lt; EOMONTH(DATE(YEAR(B246),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B246),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E246" s="1">
@@ -9282,20 +6165,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D247" s="9" t="str">
-        <f>IF(
- AND(
-  B247 &gt;= EOMONTH(DATE(YEAR(B247),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B247),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B247 &lt; EOMONTH(DATE(YEAR(B247),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B247),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E247" s="1">
@@ -9319,20 +6189,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D248" s="9" t="str">
-        <f>IF(
- AND(
-  B248 &gt;= EOMONTH(DATE(YEAR(B248),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B248),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B248 &lt; EOMONTH(DATE(YEAR(B248),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B248),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E248" s="1">
@@ -9356,20 +6213,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D249" s="9" t="str">
-        <f>IF(
- AND(
-  B249 &gt;= EOMONTH(DATE(YEAR(B249),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B249),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B249 &lt; EOMONTH(DATE(YEAR(B249),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B249),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E249" s="1">
@@ -9393,20 +6237,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D250" s="9" t="str">
-        <f>IF(
- AND(
-  B250 &gt;= EOMONTH(DATE(YEAR(B250),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B250),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B250 &lt; EOMONTH(DATE(YEAR(B250),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B250),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E250" s="1">
@@ -9430,20 +6261,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D251" s="9" t="str">
-        <f>IF(
- AND(
-  B251 &gt;= EOMONTH(DATE(YEAR(B251),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B251),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B251 &lt; EOMONTH(DATE(YEAR(B251),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B251),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
       <c r="E251" s="1">
@@ -9467,20 +6285,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D252" s="9" t="str">
-        <f>IF(
- AND(
-  B252 &gt;= EOMONTH(DATE(YEAR(B252),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B252),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B252 &lt; EOMONTH(DATE(YEAR(B252),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B252),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E252" s="1">
@@ -9504,20 +6309,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D253" s="9" t="str">
-        <f>IF(
- AND(
-  B253 &gt;= EOMONTH(DATE(YEAR(B253),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B253),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B253 &lt; EOMONTH(DATE(YEAR(B253),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B253),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E253" s="1">
@@ -9541,20 +6333,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D254" s="9" t="str">
-        <f>IF(
- AND(
-  B254 &gt;= EOMONTH(DATE(YEAR(B254),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B254),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B254 &lt; EOMONTH(DATE(YEAR(B254),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B254),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E254" s="1">
@@ -9578,20 +6357,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D255" s="9" t="str">
-        <f>IF(
- AND(
-  B255 &gt;= EOMONTH(DATE(YEAR(B255),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B255),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B255 &lt; EOMONTH(DATE(YEAR(B255),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B255),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E255" s="1">
@@ -9615,20 +6381,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D256" s="9" t="str">
-        <f>IF(
- AND(
-  B256 &gt;= EOMONTH(DATE(YEAR(B256),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B256),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B256 &lt; EOMONTH(DATE(YEAR(B256),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B256),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E256" s="1">
@@ -9652,20 +6405,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D257" s="9" t="str">
-        <f>IF(
- AND(
-  B257 &gt;= EOMONTH(DATE(YEAR(B257),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B257),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B257 &lt; EOMONTH(DATE(YEAR(B257),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B257),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
       <c r="E257" s="1">
@@ -9689,7 +6429,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D258" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="D258:D321" si="4">IF(
  AND(
   B258 &gt;= EOMONTH(DATE(YEAR(B258),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B258),3,1),0),1)
@@ -9726,20 +6466,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D259" s="9" t="str">
-        <f>IF(
- AND(
-  B259 &gt;= EOMONTH(DATE(YEAR(B259),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B259),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B259 &lt; EOMONTH(DATE(YEAR(B259),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B259),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E259" s="1">
@@ -9763,20 +6490,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D260" s="9" t="str">
-        <f>IF(
- AND(
-  B260 &gt;= EOMONTH(DATE(YEAR(B260),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B260),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B260 &lt; EOMONTH(DATE(YEAR(B260),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B260),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E260" s="1">
@@ -9800,20 +6514,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D261" s="9" t="str">
-        <f>IF(
- AND(
-  B261 &gt;= EOMONTH(DATE(YEAR(B261),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B261),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B261 &lt; EOMONTH(DATE(YEAR(B261),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B261),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E261" s="1">
@@ -9837,20 +6538,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D262" s="9" t="str">
-        <f>IF(
- AND(
-  B262 &gt;= EOMONTH(DATE(YEAR(B262),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B262),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B262 &lt; EOMONTH(DATE(YEAR(B262),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B262),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E262" s="1">
@@ -9874,20 +6562,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D263" s="9" t="str">
-        <f>IF(
- AND(
-  B263 &gt;= EOMONTH(DATE(YEAR(B263),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B263),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B263 &lt; EOMONTH(DATE(YEAR(B263),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B263),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E263" s="1">
@@ -9911,20 +6586,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D264" s="9" t="str">
-        <f>IF(
- AND(
-  B264 &gt;= EOMONTH(DATE(YEAR(B264),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B264),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B264 &lt; EOMONTH(DATE(YEAR(B264),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B264),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E264" s="1">
@@ -9948,20 +6610,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D265" s="9" t="str">
-        <f>IF(
- AND(
-  B265 &gt;= EOMONTH(DATE(YEAR(B265),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B265),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B265 &lt; EOMONTH(DATE(YEAR(B265),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B265),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E265" s="1">
@@ -9985,20 +6634,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D266" s="9" t="str">
-        <f>IF(
- AND(
-  B266 &gt;= EOMONTH(DATE(YEAR(B266),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B266),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B266 &lt; EOMONTH(DATE(YEAR(B266),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B266),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E266" s="1">
@@ -10022,20 +6658,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D267" s="9" t="str">
-        <f>IF(
- AND(
-  B267 &gt;= EOMONTH(DATE(YEAR(B267),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B267),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B267 &lt; EOMONTH(DATE(YEAR(B267),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B267),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E267" s="1">
@@ -10059,20 +6682,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D268" s="9" t="str">
-        <f>IF(
- AND(
-  B268 &gt;= EOMONTH(DATE(YEAR(B268),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B268),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B268 &lt; EOMONTH(DATE(YEAR(B268),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B268),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E268" s="1">
@@ -10096,20 +6706,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D269" s="9" t="str">
-        <f>IF(
- AND(
-  B269 &gt;= EOMONTH(DATE(YEAR(B269),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B269),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B269 &lt; EOMONTH(DATE(YEAR(B269),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B269),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E269" s="1">
@@ -10133,20 +6730,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D270" s="9" t="str">
-        <f>IF(
- AND(
-  B270 &gt;= EOMONTH(DATE(YEAR(B270),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B270),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B270 &lt; EOMONTH(DATE(YEAR(B270),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B270),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E270" s="1">
@@ -10170,20 +6754,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D271" s="9" t="str">
-        <f>IF(
- AND(
-  B271 &gt;= EOMONTH(DATE(YEAR(B271),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B271),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B271 &lt; EOMONTH(DATE(YEAR(B271),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B271),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E271" s="1">
@@ -10207,20 +6778,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D272" s="9" t="str">
-        <f>IF(
- AND(
-  B272 &gt;= EOMONTH(DATE(YEAR(B272),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B272),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B272 &lt; EOMONTH(DATE(YEAR(B272),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B272),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E272" s="1">
@@ -10244,20 +6802,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D273" s="9" t="str">
-        <f>IF(
- AND(
-  B273 &gt;= EOMONTH(DATE(YEAR(B273),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B273),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B273 &lt; EOMONTH(DATE(YEAR(B273),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B273),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E273" s="1">
@@ -10281,20 +6826,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D274" s="9" t="str">
-        <f>IF(
- AND(
-  B274 &gt;= EOMONTH(DATE(YEAR(B274),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B274),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B274 &lt; EOMONTH(DATE(YEAR(B274),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B274),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E274" s="1">
@@ -10318,20 +6850,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D275" s="9" t="str">
-        <f>IF(
- AND(
-  B275 &gt;= EOMONTH(DATE(YEAR(B275),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B275),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B275 &lt; EOMONTH(DATE(YEAR(B275),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B275),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E275" s="1">
@@ -10355,20 +6874,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D276" s="9" t="str">
-        <f>IF(
- AND(
-  B276 &gt;= EOMONTH(DATE(YEAR(B276),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B276),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B276 &lt; EOMONTH(DATE(YEAR(B276),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B276),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E276" s="1">
@@ -10392,20 +6898,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D277" s="9" t="str">
-        <f>IF(
- AND(
-  B277 &gt;= EOMONTH(DATE(YEAR(B277),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B277),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B277 &lt; EOMONTH(DATE(YEAR(B277),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B277),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E277" s="1">
@@ -10429,20 +6922,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D278" s="9" t="str">
-        <f>IF(
- AND(
-  B278 &gt;= EOMONTH(DATE(YEAR(B278),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B278),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B278 &lt; EOMONTH(DATE(YEAR(B278),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B278),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E278" s="1">
@@ -10466,20 +6946,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D279" s="9" t="str">
-        <f>IF(
- AND(
-  B279 &gt;= EOMONTH(DATE(YEAR(B279),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B279),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B279 &lt; EOMONTH(DATE(YEAR(B279),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B279),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E279" s="1">
@@ -10503,20 +6970,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D280" s="9" t="str">
-        <f>IF(
- AND(
-  B280 &gt;= EOMONTH(DATE(YEAR(B280),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B280),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B280 &lt; EOMONTH(DATE(YEAR(B280),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B280),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E280" s="1">
@@ -10540,20 +6994,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D281" s="9" t="str">
-        <f>IF(
- AND(
-  B281 &gt;= EOMONTH(DATE(YEAR(B281),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B281),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B281 &lt; EOMONTH(DATE(YEAR(B281),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B281),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E281" s="1">
@@ -10577,20 +7018,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D282" s="9" t="str">
-        <f>IF(
- AND(
-  B282 &gt;= EOMONTH(DATE(YEAR(B282),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B282),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B282 &lt; EOMONTH(DATE(YEAR(B282),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B282),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E282" s="1">
@@ -10614,20 +7042,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D283" s="9" t="str">
-        <f>IF(
- AND(
-  B283 &gt;= EOMONTH(DATE(YEAR(B283),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B283),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B283 &lt; EOMONTH(DATE(YEAR(B283),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B283),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E283" s="1">
@@ -10651,20 +7066,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D284" s="9" t="str">
-        <f>IF(
- AND(
-  B284 &gt;= EOMONTH(DATE(YEAR(B284),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B284),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B284 &lt; EOMONTH(DATE(YEAR(B284),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B284),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E284" s="1">
@@ -10688,20 +7090,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D285" s="9" t="str">
-        <f>IF(
- AND(
-  B285 &gt;= EOMONTH(DATE(YEAR(B285),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B285),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B285 &lt; EOMONTH(DATE(YEAR(B285),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B285),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E285" s="1">
@@ -10725,20 +7114,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D286" s="9" t="str">
-        <f>IF(
- AND(
-  B286 &gt;= EOMONTH(DATE(YEAR(B286),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B286),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B286 &lt; EOMONTH(DATE(YEAR(B286),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B286),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E286" s="1">
@@ -10762,20 +7138,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D287" s="9" t="str">
-        <f>IF(
- AND(
-  B287 &gt;= EOMONTH(DATE(YEAR(B287),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B287),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B287 &lt; EOMONTH(DATE(YEAR(B287),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B287),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E287" s="1">
@@ -10799,20 +7162,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D288" s="9" t="str">
-        <f>IF(
- AND(
-  B288 &gt;= EOMONTH(DATE(YEAR(B288),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B288),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B288 &lt; EOMONTH(DATE(YEAR(B288),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B288),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E288" s="1">
@@ -10836,20 +7186,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D289" s="9" t="str">
-        <f>IF(
- AND(
-  B289 &gt;= EOMONTH(DATE(YEAR(B289),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B289),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B289 &lt; EOMONTH(DATE(YEAR(B289),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B289),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E289" s="1">
@@ -10873,20 +7210,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D290" s="9" t="str">
-        <f>IF(
- AND(
-  B290 &gt;= EOMONTH(DATE(YEAR(B290),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B290),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B290 &lt; EOMONTH(DATE(YEAR(B290),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B290),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E290" s="1">
@@ -10910,20 +7234,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D291" s="9" t="str">
-        <f>IF(
- AND(
-  B291 &gt;= EOMONTH(DATE(YEAR(B291),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B291),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B291 &lt; EOMONTH(DATE(YEAR(B291),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B291),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E291" s="1">
@@ -10947,20 +7258,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D292" s="9" t="str">
-        <f>IF(
- AND(
-  B292 &gt;= EOMONTH(DATE(YEAR(B292),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B292),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B292 &lt; EOMONTH(DATE(YEAR(B292),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B292),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E292" s="1">
@@ -10984,20 +7282,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D293" s="9" t="str">
-        <f>IF(
- AND(
-  B293 &gt;= EOMONTH(DATE(YEAR(B293),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B293),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B293 &lt; EOMONTH(DATE(YEAR(B293),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B293),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E293" s="1">
@@ -11021,20 +7306,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D294" s="9" t="str">
-        <f>IF(
- AND(
-  B294 &gt;= EOMONTH(DATE(YEAR(B294),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B294),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B294 &lt; EOMONTH(DATE(YEAR(B294),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B294),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E294" s="1">
@@ -11058,20 +7330,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D295" s="9" t="str">
-        <f>IF(
- AND(
-  B295 &gt;= EOMONTH(DATE(YEAR(B295),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B295),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B295 &lt; EOMONTH(DATE(YEAR(B295),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B295),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E295" s="1">
@@ -11095,20 +7354,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D296" s="9" t="str">
-        <f>IF(
- AND(
-  B296 &gt;= EOMONTH(DATE(YEAR(B296),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B296),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B296 &lt; EOMONTH(DATE(YEAR(B296),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B296),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E296" s="1">
@@ -11132,20 +7378,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D297" s="9" t="str">
-        <f>IF(
- AND(
-  B297 &gt;= EOMONTH(DATE(YEAR(B297),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B297),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B297 &lt; EOMONTH(DATE(YEAR(B297),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B297),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E297" s="1">
@@ -11169,20 +7402,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D298" s="9" t="str">
-        <f>IF(
- AND(
-  B298 &gt;= EOMONTH(DATE(YEAR(B298),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B298),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B298 &lt; EOMONTH(DATE(YEAR(B298),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B298),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E298" s="1">
@@ -11206,20 +7426,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D299" s="9" t="str">
-        <f>IF(
- AND(
-  B299 &gt;= EOMONTH(DATE(YEAR(B299),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B299),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B299 &lt; EOMONTH(DATE(YEAR(B299),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B299),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E299" s="1">
@@ -11243,20 +7450,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D300" s="9" t="str">
-        <f>IF(
- AND(
-  B300 &gt;= EOMONTH(DATE(YEAR(B300),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B300),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B300 &lt; EOMONTH(DATE(YEAR(B300),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B300),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E300" s="1">
@@ -11280,20 +7474,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D301" s="9" t="str">
-        <f>IF(
- AND(
-  B301 &gt;= EOMONTH(DATE(YEAR(B301),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B301),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B301 &lt; EOMONTH(DATE(YEAR(B301),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B301),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E301" s="1">
@@ -11317,20 +7498,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D302" s="9" t="str">
-        <f>IF(
- AND(
-  B302 &gt;= EOMONTH(DATE(YEAR(B302),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B302),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B302 &lt; EOMONTH(DATE(YEAR(B302),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B302),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E302" s="1">
@@ -11354,20 +7522,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D303" s="9" t="str">
-        <f>IF(
- AND(
-  B303 &gt;= EOMONTH(DATE(YEAR(B303),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B303),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B303 &lt; EOMONTH(DATE(YEAR(B303),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B303),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E303" s="1">
@@ -11391,20 +7546,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D304" s="9" t="str">
-        <f>IF(
- AND(
-  B304 &gt;= EOMONTH(DATE(YEAR(B304),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B304),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B304 &lt; EOMONTH(DATE(YEAR(B304),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B304),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E304" s="1">
@@ -11428,20 +7570,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D305" s="9" t="str">
-        <f>IF(
- AND(
-  B305 &gt;= EOMONTH(DATE(YEAR(B305),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B305),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B305 &lt; EOMONTH(DATE(YEAR(B305),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B305),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E305" s="1">
@@ -11465,20 +7594,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D306" s="9" t="str">
-        <f>IF(
- AND(
-  B306 &gt;= EOMONTH(DATE(YEAR(B306),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B306),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B306 &lt; EOMONTH(DATE(YEAR(B306),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B306),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E306" s="1">
@@ -11502,20 +7618,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D307" s="9" t="str">
-        <f>IF(
- AND(
-  B307 &gt;= EOMONTH(DATE(YEAR(B307),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B307),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B307 &lt; EOMONTH(DATE(YEAR(B307),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B307),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E307" s="1">
@@ -11539,20 +7642,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D308" s="9" t="str">
-        <f>IF(
- AND(
-  B308 &gt;= EOMONTH(DATE(YEAR(B308),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B308),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B308 &lt; EOMONTH(DATE(YEAR(B308),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B308),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E308" s="1">
@@ -11576,20 +7666,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D309" s="9" t="str">
-        <f>IF(
- AND(
-  B309 &gt;= EOMONTH(DATE(YEAR(B309),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B309),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B309 &lt; EOMONTH(DATE(YEAR(B309),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B309),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E309" s="1">
@@ -11613,20 +7690,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D310" s="9" t="str">
-        <f>IF(
- AND(
-  B310 &gt;= EOMONTH(DATE(YEAR(B310),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B310),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B310 &lt; EOMONTH(DATE(YEAR(B310),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B310),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E310" s="1">
@@ -11650,20 +7714,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D311" s="9" t="str">
-        <f>IF(
- AND(
-  B311 &gt;= EOMONTH(DATE(YEAR(B311),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B311),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B311 &lt; EOMONTH(DATE(YEAR(B311),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B311),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E311" s="1">
@@ -11687,20 +7738,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D312" s="9" t="str">
-        <f>IF(
- AND(
-  B312 &gt;= EOMONTH(DATE(YEAR(B312),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B312),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B312 &lt; EOMONTH(DATE(YEAR(B312),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B312),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E312" s="1">
@@ -11724,20 +7762,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D313" s="9" t="str">
-        <f>IF(
- AND(
-  B313 &gt;= EOMONTH(DATE(YEAR(B313),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B313),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B313 &lt; EOMONTH(DATE(YEAR(B313),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B313),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E313" s="1">
@@ -11761,20 +7786,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D314" s="9" t="str">
-        <f>IF(
- AND(
-  B314 &gt;= EOMONTH(DATE(YEAR(B314),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B314),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B314 &lt; EOMONTH(DATE(YEAR(B314),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B314),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E314" s="1">
@@ -11798,20 +7810,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D315" s="9" t="str">
-        <f>IF(
- AND(
-  B315 &gt;= EOMONTH(DATE(YEAR(B315),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B315),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B315 &lt; EOMONTH(DATE(YEAR(B315),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B315),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E315" s="1">
@@ -11835,20 +7834,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D316" s="9" t="str">
-        <f>IF(
- AND(
-  B316 &gt;= EOMONTH(DATE(YEAR(B316),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B316),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B316 &lt; EOMONTH(DATE(YEAR(B316),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B316),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E316" s="1">
@@ -11872,20 +7858,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D317" s="9" t="str">
-        <f>IF(
- AND(
-  B317 &gt;= EOMONTH(DATE(YEAR(B317),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B317),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B317 &lt; EOMONTH(DATE(YEAR(B317),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B317),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E317" s="1">
@@ -11909,20 +7882,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D318" s="9" t="str">
-        <f>IF(
- AND(
-  B318 &gt;= EOMONTH(DATE(YEAR(B318),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B318),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B318 &lt; EOMONTH(DATE(YEAR(B318),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B318),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
       <c r="E318" s="1">
@@ -11946,20 +7906,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D319" s="9" t="str">
-        <f>IF(
- AND(
-  B319 &gt;= EOMONTH(DATE(YEAR(B319),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B319),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B319 &lt; EOMONTH(DATE(YEAR(B319),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B319),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E319" s="1">
@@ -11983,20 +7930,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D320" s="9" t="str">
-        <f>IF(
- AND(
-  B320 &gt;= EOMONTH(DATE(YEAR(B320),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B320),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B320 &lt; EOMONTH(DATE(YEAR(B320),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B320),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E320" s="1">
@@ -12020,20 +7954,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D321" s="9" t="str">
-        <f>IF(
- AND(
-  B321 &gt;= EOMONTH(DATE(YEAR(B321),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B321),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B321 &lt; EOMONTH(DATE(YEAR(B321),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B321),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
       <c r="E321" s="1">
@@ -12057,7 +7978,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D322" s="9" t="str">
-        <f>IF(
+        <f t="shared" ref="D322:D340" si="5">IF(
  AND(
   B322 &gt;= EOMONTH(DATE(YEAR(B322),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B322),3,1),0),1)
@@ -12094,20 +8015,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D323" s="9" t="str">
-        <f>IF(
- AND(
-  B323 &gt;= EOMONTH(DATE(YEAR(B323),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B323),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B323 &lt; EOMONTH(DATE(YEAR(B323),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B323),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
       <c r="E323" s="1">
@@ -12131,20 +8039,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D324" s="9" t="str">
-        <f>IF(
- AND(
-  B324 &gt;= EOMONTH(DATE(YEAR(B324),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B324),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B324 &lt; EOMONTH(DATE(YEAR(B324),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B324),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E324" s="1">
@@ -12168,20 +8063,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D325" s="9" t="str">
-        <f>IF(
- AND(
-  B325 &gt;= EOMONTH(DATE(YEAR(B325),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B325),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B325 &lt; EOMONTH(DATE(YEAR(B325),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B325),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E325" s="1">
@@ -12205,20 +8087,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D326" s="9" t="str">
-        <f>IF(
- AND(
-  B326 &gt;= EOMONTH(DATE(YEAR(B326),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B326),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B326 &lt; EOMONTH(DATE(YEAR(B326),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B326),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E326" s="1">
@@ -12242,20 +8111,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D327" s="9" t="str">
-        <f>IF(
- AND(
-  B327 &gt;= EOMONTH(DATE(YEAR(B327),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B327),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B327 &lt; EOMONTH(DATE(YEAR(B327),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B327),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E327" s="1">
@@ -12279,20 +8135,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D328" s="9" t="str">
-        <f>IF(
- AND(
-  B328 &gt;= EOMONTH(DATE(YEAR(B328),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B328),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B328 &lt; EOMONTH(DATE(YEAR(B328),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B328),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E328" s="1">
@@ -12316,20 +8159,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D329" s="9" t="str">
-        <f>IF(
- AND(
-  B329 &gt;= EOMONTH(DATE(YEAR(B329),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B329),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B329 &lt; EOMONTH(DATE(YEAR(B329),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B329),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E329" s="1">
@@ -12353,20 +8183,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D330" s="9" t="str">
-        <f>IF(
- AND(
-  B330 &gt;= EOMONTH(DATE(YEAR(B330),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B330),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B330 &lt; EOMONTH(DATE(YEAR(B330),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B330),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E330" s="1">
@@ -12390,20 +8207,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D331" s="9" t="str">
-        <f>IF(
- AND(
-  B331 &gt;= EOMONTH(DATE(YEAR(B331),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B331),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B331 &lt; EOMONTH(DATE(YEAR(B331),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B331),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
       <c r="E331" s="1">
@@ -12427,20 +8231,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D332" s="9" t="str">
-        <f>IF(
- AND(
-  B332 &gt;= EOMONTH(DATE(YEAR(B332),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B332),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B332 &lt; EOMONTH(DATE(YEAR(B332),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B332),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
       <c r="E332" s="1">
@@ -12464,20 +8255,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D333" s="9" t="str">
-        <f>IF(
- AND(
-  B333 &gt;= EOMONTH(DATE(YEAR(B333),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B333),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B333 &lt; EOMONTH(DATE(YEAR(B333),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B333),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
       <c r="E333" s="1">
@@ -12501,20 +8279,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D334" s="9" t="str">
-        <f>IF(
- AND(
-  B334 &gt;= EOMONTH(DATE(YEAR(B334),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B334),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B334 &lt; EOMONTH(DATE(YEAR(B334),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B334),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
       <c r="E334" s="1">
@@ -12538,20 +8303,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D335" s="9" t="str">
-        <f>IF(
- AND(
-  B335 &gt;= EOMONTH(DATE(YEAR(B335),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B335),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B335 &lt; EOMONTH(DATE(YEAR(B335),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B335),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
       <c r="E335" s="1">
@@ -12575,20 +8327,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D336" s="9" t="str">
-        <f>IF(
- AND(
-  B336 &gt;= EOMONTH(DATE(YEAR(B336),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B336),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B336 &lt; EOMONTH(DATE(YEAR(B336),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B336),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E336" s="1">
@@ -12612,20 +8351,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D337" s="9" t="str">
-        <f>IF(
- AND(
-  B337 &gt;= EOMONTH(DATE(YEAR(B337),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B337),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B337 &lt; EOMONTH(DATE(YEAR(B337),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B337),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E337" s="1">
@@ -12649,20 +8375,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D338" s="9" t="str">
-        <f>IF(
- AND(
-  B338 &gt;= EOMONTH(DATE(YEAR(B338),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B338),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B338 &lt; EOMONTH(DATE(YEAR(B338),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B338),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E338" s="1">
@@ -12686,20 +8399,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D339" s="9" t="str">
-        <f>IF(
- AND(
-  B339 &gt;= EOMONTH(DATE(YEAR(B339),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B339),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B339 &lt; EOMONTH(DATE(YEAR(B339),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B339),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="E339" s="1">
@@ -12723,20 +8423,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D340" s="9" t="str">
-        <f>IF(
- AND(
-  B340 &gt;= EOMONTH(DATE(YEAR(B340),3,1),0)
-        - WEEKDAY(EOMONTH(DATE(YEAR(B340),3,1),0),1)
-        + 1
-        + TIME(2,0,0),
-  B340 &lt; EOMONTH(DATE(YEAR(B340),10,1),0)
-       - WEEKDAY(EOMONTH(DATE(YEAR(B340),10,1),0),1)
-       + 1
-       + TIME(3,0,0)
- ),
- "UTC+2",
- "UTC+1"
-)</f>
+        <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
       <c r="F340" s="1">
@@ -12767,16 +8454,16 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
@@ -12784,10 +8471,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>7</v>
@@ -12795,6 +8482,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{5B793FB2-62E4-449D-983A-D431BCD8A049}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_lake/macro/Europe/Employment.xlsx
+++ b/data_lake/macro/Europe/Employment.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Europe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9474952E-D846-425A-BDFF-EF60C33F7900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CD0D66-FFE5-499F-A684-C6D3FCA4A8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="912" yWindow="1812" windowWidth="21600" windowHeight="10872" activeTab="1" xr2:uid="{484F5785-4531-4BC2-998A-8344EB3D0817}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{484F5785-4531-4BC2-998A-8344EB3D0817}"/>
   </bookViews>
   <sheets>
-    <sheet name="EURUEMEM" sheetId="1" r:id="rId1"/>
-    <sheet name="info" sheetId="2" r:id="rId2"/>
+    <sheet name="info" sheetId="2" r:id="rId1"/>
+    <sheet name="EURUEMEM" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Release Date</t>
   </si>
@@ -85,6 +85,22 @@
   </si>
   <si>
     <t>https://kr.investing.com/economic-calendar/unemployment-rate-299</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exchange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EUROSTAT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Europe</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -190,7 +206,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -227,10 +243,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -548,6 +567,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0884B18C-3BF8-4D0D-AF13-B440F7F5DC83}">
+  <dimension ref="B2:G3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{5B793FB2-62E4-449D-983A-D431BCD8A049}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD80D3B9-6A9C-429A-930F-1E9445C3CEE3}">
   <dimension ref="A1:G340"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8426,6 +8505,9 @@
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
+      <c r="E340" s="1">
+        <v>6.3E-2</v>
+      </c>
       <c r="F340" s="1">
         <v>6.2E-2</v>
       </c>
@@ -8440,51 +8522,4 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0884B18C-3BF8-4D0D-AF13-B440F7F5DC83}">
-  <dimension ref="B2:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="67.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="11">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{5B793FB2-62E4-449D-983A-D431BCD8A049}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data_lake/macro/Europe/Employment.xlsx
+++ b/data_lake/macro/Europe/Employment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Europe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CD0D66-FFE5-499F-A684-C6D3FCA4A8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2022627E-52AD-43C3-A94F-C3F412230534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{484F5785-4531-4BC2-998A-8344EB3D0817}"/>
   </bookViews>
@@ -64,10 +64,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Source</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>EURUEMEM</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -101,6 +97,10 @@
   </si>
   <si>
     <t>Europe</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ticker</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -206,7 +206,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -247,9 +247,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -579,22 +576,22 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>14</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
@@ -602,19 +599,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -671,7 +668,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D2" s="9" t="str">
-        <f t="shared" ref="D2:D65" si="0">IF(
+        <f>IF(
  AND(
   B2 &gt;= EOMONTH(DATE(YEAR(B2),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B2),3,1),0),1)
@@ -703,7 +700,20 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D3" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D2:D65" si="0">IF(
+ AND(
+  B3 &gt;= EOMONTH(DATE(YEAR(B3),3,1),0)
+        - WEEKDAY(EOMONTH(DATE(YEAR(B3),3,1),0),1)
+        + 1
+        + TIME(2,0,0),
+  B3 &lt; EOMONTH(DATE(YEAR(B3),10,1),0)
+       - WEEKDAY(EOMONTH(DATE(YEAR(B3),10,1),0),1)
+       + 1
+       + TIME(3,0,0)
+ ),
+ "UTC+2",
+ "UTC+1"
+)</f>
         <v>UTC+2</v>
       </c>
       <c r="E3" s="1">

--- a/data_lake/macro/Europe/Employment.xlsx
+++ b/data_lake/macro/Europe/Employment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Europe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/Europe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2022627E-52AD-43C3-A94F-C3F412230534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C8FA8A-BD7B-E74E-91B0-4510F219866E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{484F5785-4531-4BC2-998A-8344EB3D0817}"/>
+    <workbookView xWindow="17980" yWindow="780" windowWidth="18020" windowHeight="20800" activeTab="1" xr2:uid="{484F5785-4531-4BC2-998A-8344EB3D0817}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="2" r:id="rId1"/>
@@ -109,9 +109,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="178" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -143,7 +143,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -206,32 +206,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -249,11 +237,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -269,9 +263,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -309,7 +303,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -415,7 +409,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -557,7 +551,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -566,51 +560,51 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0884B18C-3BF8-4D0D-AF13-B440F7F5DC83}">
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="67.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="11">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -625,49 +619,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD80D3B9-6A9C-429A-930F-1E9445C3CEE3}">
-  <dimension ref="A1:G340"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G341"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="11">
         <v>35886</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="11">
         <v>35916</v>
       </c>
-      <c r="C2" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="9" t="str">
+      <c r="C2" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="5" t="str">
         <f>IF(
  AND(
   B2 &gt;= EOMONTH(DATE(YEAR(B2),3,1),0)
@@ -689,18 +683,18 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="11">
         <v>35916</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="11">
         <v>35947</v>
       </c>
-      <c r="C3" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="9" t="str">
-        <f t="shared" ref="D2:D65" si="0">IF(
+      <c r="C3" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f t="shared" ref="D3:D65" si="0">IF(
  AND(
   B3 &gt;= EOMONTH(DATE(YEAR(B3),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B3),3,1),0),1)
@@ -723,17 +717,17 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
         <v>35947</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="11">
         <v>35977</v>
       </c>
-      <c r="C4" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="9" t="str">
+      <c r="C4" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -744,17 +738,17 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
         <v>35977</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="11">
         <v>36008</v>
       </c>
-      <c r="C5" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="9" t="str">
+      <c r="C5" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -765,17 +759,17 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
         <v>36008</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="11">
         <v>36039</v>
       </c>
-      <c r="C6" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="9" t="str">
+      <c r="C6" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -786,17 +780,17 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
         <v>36039</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="11">
         <v>36069</v>
       </c>
-      <c r="C7" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="9" t="str">
+      <c r="C7" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -807,17 +801,17 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
         <v>36069</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="11">
         <v>36100</v>
       </c>
-      <c r="C8" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="9" t="str">
+      <c r="C8" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -828,17 +822,17 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
         <v>36100</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="11">
         <v>36130</v>
       </c>
-      <c r="C9" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="9" t="str">
+      <c r="C9" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -849,17 +843,17 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
         <v>36130</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="11">
         <v>36161</v>
       </c>
-      <c r="C10" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="9" t="str">
+      <c r="C10" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -870,17 +864,17 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="11">
         <v>36161</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="11">
         <v>36192</v>
       </c>
-      <c r="C11" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="9" t="str">
+      <c r="C11" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -891,17 +885,17 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="11">
         <v>36192</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="11">
         <v>36220</v>
       </c>
-      <c r="C12" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D12" s="9" t="str">
+      <c r="C12" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -912,17 +906,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
         <v>36220</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="11">
         <v>36251</v>
       </c>
-      <c r="C13" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D13" s="9" t="str">
+      <c r="C13" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -933,17 +927,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="6">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
         <v>36251</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="11">
         <v>36281</v>
       </c>
-      <c r="C14" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="9" t="str">
+      <c r="C14" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -954,17 +948,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="6">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
         <v>36281</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="11">
         <v>36312</v>
       </c>
-      <c r="C15" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D15" s="9" t="str">
+      <c r="C15" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -975,17 +969,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="6">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
         <v>36312</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="11">
         <v>36342</v>
       </c>
-      <c r="C16" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D16" s="9" t="str">
+      <c r="C16" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -996,17 +990,17 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="6">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
         <v>36342</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="11">
         <v>36373</v>
       </c>
-      <c r="C17" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D17" s="9" t="str">
+      <c r="C17" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1017,17 +1011,17 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="6">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
         <v>36373</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="11">
         <v>36404</v>
       </c>
-      <c r="C18" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="9" t="str">
+      <c r="C18" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1038,17 +1032,17 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="6">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
         <v>36404</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="11">
         <v>36434</v>
       </c>
-      <c r="C19" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D19" s="9" t="str">
+      <c r="C19" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1059,17 +1053,17 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="6">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
         <v>36434</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="11">
         <v>36465</v>
       </c>
-      <c r="C20" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D20" s="9" t="str">
+      <c r="C20" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D20" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1080,17 +1074,17 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="6">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="11">
         <v>36465</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="11">
         <v>36495</v>
       </c>
-      <c r="C21" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D21" s="9" t="str">
+      <c r="C21" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D21" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1101,17 +1095,17 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="6">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="11">
         <v>36495</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="11">
         <v>36526</v>
       </c>
-      <c r="C22" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D22" s="9" t="str">
+      <c r="C22" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1122,17 +1116,17 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="6">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="11">
         <v>36526</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="11">
         <v>36557</v>
       </c>
-      <c r="C23" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D23" s="9" t="str">
+      <c r="C23" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1143,17 +1137,17 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="6">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="11">
         <v>36557</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="11">
         <v>36586</v>
       </c>
-      <c r="C24" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D24" s="9" t="str">
+      <c r="C24" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1164,17 +1158,17 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="6">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="11">
         <v>36586</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="11">
         <v>36617</v>
       </c>
-      <c r="C25" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="9" t="str">
+      <c r="C25" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1185,17 +1179,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="6">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="11">
         <v>36617</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="11">
         <v>36647</v>
       </c>
-      <c r="C26" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D26" s="9" t="str">
+      <c r="C26" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D26" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1206,17 +1200,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="6">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="11">
         <v>36647</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="11">
         <v>36678</v>
       </c>
-      <c r="C27" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D27" s="9" t="str">
+      <c r="C27" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D27" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1227,17 +1221,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="6">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="11">
         <v>36678</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="11">
         <v>36708</v>
       </c>
-      <c r="C28" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D28" s="9" t="str">
+      <c r="C28" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1248,17 +1242,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="6">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="11">
         <v>36708</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="11">
         <v>36739</v>
       </c>
-      <c r="C29" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D29" s="9" t="str">
+      <c r="C29" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1269,17 +1263,17 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="6">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="11">
         <v>36739</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="11">
         <v>36770</v>
       </c>
-      <c r="C30" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D30" s="9" t="str">
+      <c r="C30" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1290,17 +1284,17 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="6">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="11">
         <v>36770</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="11">
         <v>36800</v>
       </c>
-      <c r="C31" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D31" s="9" t="str">
+      <c r="C31" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1311,17 +1305,17 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="6">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="11">
         <v>36800</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="11">
         <v>36831</v>
       </c>
-      <c r="C32" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D32" s="9" t="str">
+      <c r="C32" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1332,17 +1326,17 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="6">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="11">
         <v>36831</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="11">
         <v>36861</v>
       </c>
-      <c r="C33" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D33" s="9" t="str">
+      <c r="C33" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1353,17 +1347,17 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="6">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="11">
         <v>36861</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="11">
         <v>36892</v>
       </c>
-      <c r="C34" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D34" s="9" t="str">
+      <c r="C34" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D34" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1374,17 +1368,17 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="6">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="11">
         <v>36892</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="11">
         <v>36923</v>
       </c>
-      <c r="C35" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D35" s="9" t="str">
+      <c r="C35" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D35" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1395,17 +1389,17 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="6">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="11">
         <v>36923</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="11">
         <v>36951</v>
       </c>
-      <c r="C36" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D36" s="9" t="str">
+      <c r="C36" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D36" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1416,17 +1410,17 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="6">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="11">
         <v>36951</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="11">
         <v>36982</v>
       </c>
-      <c r="C37" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D37" s="9" t="str">
+      <c r="C37" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D37" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1437,17 +1431,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="6">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="11">
         <v>36982</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="11">
         <v>37012</v>
       </c>
-      <c r="C38" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D38" s="9" t="str">
+      <c r="C38" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D38" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1458,17 +1452,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="6">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="11">
         <v>37012</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="11">
         <v>37043</v>
       </c>
-      <c r="C39" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D39" s="9" t="str">
+      <c r="C39" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D39" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1479,17 +1473,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="6">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="11">
         <v>37043</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="11">
         <v>37073</v>
       </c>
-      <c r="C40" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D40" s="9" t="str">
+      <c r="C40" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D40" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1500,17 +1494,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="6">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="11">
         <v>37073</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="11">
         <v>37104</v>
       </c>
-      <c r="C41" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D41" s="9" t="str">
+      <c r="C41" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D41" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1521,17 +1515,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="6">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="11">
         <v>37104</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="11">
         <v>37135</v>
       </c>
-      <c r="C42" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D42" s="9" t="str">
+      <c r="C42" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D42" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1542,17 +1536,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="6">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="11">
         <v>37135</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="11">
         <v>37165</v>
       </c>
-      <c r="C43" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D43" s="9" t="str">
+      <c r="C43" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D43" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1563,17 +1557,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="6">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="11">
         <v>37165</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="11">
         <v>37196</v>
       </c>
-      <c r="C44" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D44" s="9" t="str">
+      <c r="C44" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D44" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1584,17 +1578,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="6">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="11">
         <v>37196</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="11">
         <v>37226</v>
       </c>
-      <c r="C45" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D45" s="9" t="str">
+      <c r="C45" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D45" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1605,17 +1599,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="6">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="11">
         <v>37226</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="11">
         <v>37257</v>
       </c>
-      <c r="C46" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D46" s="9" t="str">
+      <c r="C46" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D46" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1626,17 +1620,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="6">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="11">
         <v>37257</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="11">
         <v>37288</v>
       </c>
-      <c r="C47" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D47" s="9" t="str">
+      <c r="C47" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D47" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1647,17 +1641,17 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="6">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="11">
         <v>37288</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="11">
         <v>37316</v>
       </c>
-      <c r="C48" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D48" s="9" t="str">
+      <c r="C48" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D48" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1668,17 +1662,17 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="6">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="11">
         <v>37316</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="11">
         <v>37347</v>
       </c>
-      <c r="C49" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D49" s="9" t="str">
+      <c r="C49" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D49" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1689,17 +1683,17 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="6">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="11">
         <v>37347</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="11">
         <v>37377</v>
       </c>
-      <c r="C50" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D50" s="9" t="str">
+      <c r="C50" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D50" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1710,17 +1704,17 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="6">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="11">
         <v>37377</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="11">
         <v>37408</v>
       </c>
-      <c r="C51" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D51" s="9" t="str">
+      <c r="C51" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D51" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1731,17 +1725,17 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="6">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="11">
         <v>37408</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="11">
         <v>37438</v>
       </c>
-      <c r="C52" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D52" s="9" t="str">
+      <c r="C52" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D52" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1752,17 +1746,17 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="6">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="11">
         <v>37438</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="11">
         <v>37469</v>
       </c>
-      <c r="C53" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D53" s="9" t="str">
+      <c r="C53" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D53" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1773,17 +1767,17 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="6">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="11">
         <v>37469</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="11">
         <v>37500</v>
       </c>
-      <c r="C54" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D54" s="9" t="str">
+      <c r="C54" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D54" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1794,17 +1788,17 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="6">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="11">
         <v>37500</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="11">
         <v>37530</v>
       </c>
-      <c r="C55" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D55" s="9" t="str">
+      <c r="C55" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D55" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1815,17 +1809,17 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="6">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="11">
         <v>37530</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="11">
         <v>37561</v>
       </c>
-      <c r="C56" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D56" s="9" t="str">
+      <c r="C56" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D56" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1836,17 +1830,17 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="6">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="11">
         <v>37561</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="11">
         <v>37591</v>
       </c>
-      <c r="C57" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D57" s="9" t="str">
+      <c r="C57" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D57" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1857,17 +1851,17 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="6">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="11">
         <v>37591</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="11">
         <v>37622</v>
       </c>
-      <c r="C58" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D58" s="9" t="str">
+      <c r="C58" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D58" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1878,17 +1872,17 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="6">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="11">
         <v>37622</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="11">
         <v>37653</v>
       </c>
-      <c r="C59" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D59" s="9" t="str">
+      <c r="C59" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D59" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1899,17 +1893,17 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="6">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="11">
         <v>37653</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="11">
         <v>37681</v>
       </c>
-      <c r="C60" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D60" s="9" t="str">
+      <c r="C60" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D60" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+1</v>
       </c>
@@ -1920,17 +1914,17 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="6">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="11">
         <v>37681</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="11">
         <v>37712</v>
       </c>
-      <c r="C61" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D61" s="9" t="str">
+      <c r="C61" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D61" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1941,17 +1935,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="6">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="11">
         <v>37712</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="11">
         <v>37742</v>
       </c>
-      <c r="C62" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D62" s="9" t="str">
+      <c r="C62" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D62" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1962,17 +1956,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="6">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="11">
         <v>37742</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="11">
         <v>37773</v>
       </c>
-      <c r="C63" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D63" s="9" t="str">
+      <c r="C63" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D63" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -1983,17 +1977,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="6">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="11">
         <v>37773</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="11">
         <v>37803</v>
       </c>
-      <c r="C64" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D64" s="9" t="str">
+      <c r="C64" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D64" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -2004,17 +1998,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="6">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="11">
         <v>37803</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="11">
         <v>37834</v>
       </c>
-      <c r="C65" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D65" s="9" t="str">
+      <c r="C65" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D65" s="5" t="str">
         <f t="shared" si="0"/>
         <v>UTC+2</v>
       </c>
@@ -2025,17 +2019,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="6">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="11">
         <v>37834</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="11">
         <v>37865</v>
       </c>
-      <c r="C66" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D66" s="9" t="str">
+      <c r="C66" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D66" s="5" t="str">
         <f t="shared" ref="D66:D129" si="1">IF(
  AND(
   B66 &gt;= EOMONTH(DATE(YEAR(B66),3,1),0)
@@ -2059,17 +2053,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="6">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="11">
         <v>37865</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="11">
         <v>37895</v>
       </c>
-      <c r="C67" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D67" s="9" t="str">
+      <c r="C67" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D67" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2080,17 +2074,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="6">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="11">
         <v>37895</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="11">
         <v>37926</v>
       </c>
-      <c r="C68" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D68" s="9" t="str">
+      <c r="C68" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D68" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2101,17 +2095,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="6">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="11">
         <v>37926</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="11">
         <v>37956</v>
       </c>
-      <c r="C69" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D69" s="9" t="str">
+      <c r="C69" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D69" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2122,17 +2116,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="6">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="11">
         <v>37956</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="11">
         <v>37987</v>
       </c>
-      <c r="C70" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D70" s="9" t="str">
+      <c r="C70" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D70" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2143,17 +2137,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="6">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="11">
         <v>37987</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="11">
         <v>38018</v>
       </c>
-      <c r="C71" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D71" s="9" t="str">
+      <c r="C71" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D71" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2164,17 +2158,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="6">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="11">
         <v>38018</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="11">
         <v>38047</v>
       </c>
-      <c r="C72" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D72" s="9" t="str">
+      <c r="C72" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D72" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2185,17 +2179,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="6">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="11">
         <v>38047</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73" s="11">
         <v>38078</v>
       </c>
-      <c r="C73" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D73" s="9" t="str">
+      <c r="C73" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D73" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2206,17 +2200,17 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="6">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="11">
         <v>38078</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="11">
         <v>38108</v>
       </c>
-      <c r="C74" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D74" s="9" t="str">
+      <c r="C74" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D74" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2227,17 +2221,17 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="6">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="11">
         <v>38108</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="11">
         <v>38139</v>
       </c>
-      <c r="C75" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D75" s="9" t="str">
+      <c r="C75" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D75" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2248,17 +2242,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="6">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="11">
         <v>38139</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="11">
         <v>38169</v>
       </c>
-      <c r="C76" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D76" s="9" t="str">
+      <c r="C76" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D76" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2269,17 +2263,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="6">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="11">
         <v>38169</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="11">
         <v>38200</v>
       </c>
-      <c r="C77" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D77" s="9" t="str">
+      <c r="C77" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D77" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2290,17 +2284,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="6">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="11">
         <v>38200</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="11">
         <v>38231</v>
       </c>
-      <c r="C78" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D78" s="9" t="str">
+      <c r="C78" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D78" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2311,17 +2305,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="6">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="11">
         <v>38231</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="11">
         <v>38261</v>
       </c>
-      <c r="C79" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D79" s="9" t="str">
+      <c r="C79" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D79" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2332,17 +2326,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="6">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="11">
         <v>38261</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="11">
         <v>38292</v>
       </c>
-      <c r="C80" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D80" s="9" t="str">
+      <c r="C80" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D80" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2353,17 +2347,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="6">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="11">
         <v>38292</v>
       </c>
-      <c r="B81" s="7">
+      <c r="B81" s="11">
         <v>38322</v>
       </c>
-      <c r="C81" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D81" s="9" t="str">
+      <c r="C81" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D81" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2374,17 +2368,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="6">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="11">
         <v>38322</v>
       </c>
-      <c r="B82" s="7">
+      <c r="B82" s="11">
         <v>38353</v>
       </c>
-      <c r="C82" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D82" s="9" t="str">
+      <c r="C82" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D82" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2395,17 +2389,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="6">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="11">
         <v>38353</v>
       </c>
-      <c r="B83" s="7">
+      <c r="B83" s="11">
         <v>38384</v>
       </c>
-      <c r="C83" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D83" s="9" t="str">
+      <c r="C83" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D83" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2416,17 +2410,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="6">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="11">
         <v>38384</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="11">
         <v>38412</v>
       </c>
-      <c r="C84" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D84" s="9" t="str">
+      <c r="C84" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D84" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2437,17 +2431,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="6">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="11">
         <v>38412</v>
       </c>
-      <c r="B85" s="7">
+      <c r="B85" s="11">
         <v>38443</v>
       </c>
-      <c r="C85" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D85" s="9" t="str">
+      <c r="C85" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D85" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2458,17 +2452,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="6">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="11">
         <v>38443</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="11">
         <v>38473</v>
       </c>
-      <c r="C86" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D86" s="9" t="str">
+      <c r="C86" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D86" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2479,17 +2473,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="6">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="11">
         <v>38473</v>
       </c>
-      <c r="B87" s="7">
+      <c r="B87" s="11">
         <v>38504</v>
       </c>
-      <c r="C87" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D87" s="9" t="str">
+      <c r="C87" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D87" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2500,17 +2494,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="6">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" s="11">
         <v>38504</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="11">
         <v>38534</v>
       </c>
-      <c r="C88" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D88" s="9" t="str">
+      <c r="C88" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D88" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2521,17 +2515,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="6">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="11">
         <v>38534</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89" s="11">
         <v>38565</v>
       </c>
-      <c r="C89" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D89" s="9" t="str">
+      <c r="C89" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D89" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2542,17 +2536,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="6">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="11">
         <v>38565</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="11">
         <v>38596</v>
       </c>
-      <c r="C90" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D90" s="9" t="str">
+      <c r="C90" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D90" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2563,17 +2557,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="6">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" s="11">
         <v>38596</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="11">
         <v>38626</v>
       </c>
-      <c r="C91" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D91" s="9" t="str">
+      <c r="C91" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D91" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2584,17 +2578,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="6">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="11">
         <v>38626</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="11">
         <v>38657</v>
       </c>
-      <c r="C92" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D92" s="9" t="str">
+      <c r="C92" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D92" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2605,17 +2599,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="6">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="11">
         <v>38657</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="11">
         <v>38687</v>
       </c>
-      <c r="C93" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D93" s="9" t="str">
+      <c r="C93" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D93" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2626,17 +2620,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="6">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="11">
         <v>38687</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="11">
         <v>38718</v>
       </c>
-      <c r="C94" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D94" s="9" t="str">
+      <c r="C94" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D94" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2647,17 +2641,17 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="6">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="11">
         <v>38718</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="11">
         <v>38749</v>
       </c>
-      <c r="C95" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D95" s="9" t="str">
+      <c r="C95" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D95" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2668,17 +2662,17 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="6">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" s="11">
         <v>38749</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="11">
         <v>38777</v>
       </c>
-      <c r="C96" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D96" s="9" t="str">
+      <c r="C96" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D96" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2689,17 +2683,17 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="6">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="11">
         <v>38777</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="11">
         <v>38808</v>
       </c>
-      <c r="C97" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D97" s="9" t="str">
+      <c r="C97" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D97" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2710,17 +2704,17 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="6">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="11">
         <v>38808</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="11">
         <v>38838</v>
       </c>
-      <c r="C98" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D98" s="9" t="str">
+      <c r="C98" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D98" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2731,17 +2725,17 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="6">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="11">
         <v>38838</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99" s="11">
         <v>38869</v>
       </c>
-      <c r="C99" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D99" s="9" t="str">
+      <c r="C99" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D99" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2752,17 +2746,17 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="6">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="11">
         <v>38869</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="11">
         <v>38899</v>
       </c>
-      <c r="C100" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D100" s="9" t="str">
+      <c r="C100" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D100" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2773,17 +2767,17 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="6">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" s="11">
         <v>38899</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="11">
         <v>38930</v>
       </c>
-      <c r="C101" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D101" s="9" t="str">
+      <c r="C101" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D101" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2794,17 +2788,17 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="6">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" s="11">
         <v>38930</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="11">
         <v>38961</v>
       </c>
-      <c r="C102" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D102" s="9" t="str">
+      <c r="C102" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D102" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2815,17 +2809,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="6">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" s="11">
         <v>38961</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="11">
         <v>38991</v>
       </c>
-      <c r="C103" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D103" s="9" t="str">
+      <c r="C103" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D103" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2836,17 +2830,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="6">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" s="11">
         <v>38991</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="11">
         <v>39022</v>
       </c>
-      <c r="C104" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D104" s="9" t="str">
+      <c r="C104" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D104" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2857,17 +2851,17 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="6">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="11">
         <v>39022</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="11">
         <v>39052</v>
       </c>
-      <c r="C105" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D105" s="9" t="str">
+      <c r="C105" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D105" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2878,17 +2872,17 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="6">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="11">
         <v>39052</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="11">
         <v>39083</v>
       </c>
-      <c r="C106" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D106" s="9" t="str">
+      <c r="C106" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D106" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2899,17 +2893,17 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="6">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="11">
         <v>39083</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B107" s="11">
         <v>39114</v>
       </c>
-      <c r="C107" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D107" s="9" t="str">
+      <c r="C107" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D107" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2920,17 +2914,17 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="6">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="11">
         <v>39114</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="11">
         <v>39142</v>
       </c>
-      <c r="C108" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D108" s="9" t="str">
+      <c r="C108" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D108" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -2941,17 +2935,17 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="6">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="11">
         <v>39142</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="11">
         <v>39173</v>
       </c>
-      <c r="C109" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D109" s="9" t="str">
+      <c r="C109" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D109" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2962,17 +2956,17 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="6">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="11">
         <v>39173</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="11">
         <v>39203</v>
       </c>
-      <c r="C110" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D110" s="9" t="str">
+      <c r="C110" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D110" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -2983,17 +2977,17 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="6">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="11">
         <v>39203</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="11">
         <v>39234</v>
       </c>
-      <c r="C111" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D111" s="9" t="str">
+      <c r="C111" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D111" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3004,17 +2998,17 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="6">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="11">
         <v>39234</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="11">
         <v>39264</v>
       </c>
-      <c r="C112" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D112" s="9" t="str">
+      <c r="C112" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D112" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3025,17 +3019,17 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="6">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="11">
         <v>39264</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="11">
         <v>39295</v>
       </c>
-      <c r="C113" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D113" s="9" t="str">
+      <c r="C113" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D113" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3046,17 +3040,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="6">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" s="11">
         <v>39295</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="11">
         <v>39326</v>
       </c>
-      <c r="C114" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D114" s="9" t="str">
+      <c r="C114" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D114" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3067,17 +3061,17 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="6">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" s="11">
         <v>39326</v>
       </c>
-      <c r="B115" s="7">
+      <c r="B115" s="11">
         <v>39356</v>
       </c>
-      <c r="C115" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D115" s="9" t="str">
+      <c r="C115" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D115" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3088,17 +3082,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="6">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" s="11">
         <v>39356</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="11">
         <v>39387</v>
       </c>
-      <c r="C116" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D116" s="9" t="str">
+      <c r="C116" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D116" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -3109,17 +3103,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="6">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" s="11">
         <v>39387</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="11">
         <v>39417</v>
       </c>
-      <c r="C117" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D117" s="9" t="str">
+      <c r="C117" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D117" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -3130,17 +3124,17 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="6">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" s="11">
         <v>39417</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="11">
         <v>39448</v>
       </c>
-      <c r="C118" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D118" s="9" t="str">
+      <c r="C118" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D118" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -3151,17 +3145,17 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="6">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" s="11">
         <v>39448</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="11">
         <v>39479</v>
       </c>
-      <c r="C119" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D119" s="9" t="str">
+      <c r="C119" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D119" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -3172,17 +3166,17 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="6">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" s="11">
         <v>39479</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="11">
         <v>39508</v>
       </c>
-      <c r="C120" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D120" s="9" t="str">
+      <c r="C120" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D120" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -3193,17 +3187,17 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="6">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" s="11">
         <v>39508</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="11">
         <v>39568</v>
       </c>
-      <c r="C121" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D121" s="9" t="str">
+      <c r="C121" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D121" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3217,17 +3211,17 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="6">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" s="11">
         <v>39539</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="11">
         <v>39598</v>
       </c>
-      <c r="C122" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D122" s="9" t="str">
+      <c r="C122" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D122" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3241,17 +3235,17 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="6">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" s="11">
         <v>39569</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="11">
         <v>39630</v>
       </c>
-      <c r="C123" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D123" s="9" t="str">
+      <c r="C123" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D123" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3265,17 +3259,17 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="6">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" s="11">
         <v>39600</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="11">
         <v>39660</v>
       </c>
-      <c r="C124" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D124" s="9" t="str">
+      <c r="C124" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D124" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3289,17 +3283,17 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="6">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" s="11">
         <v>39630</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="11">
         <v>39689</v>
       </c>
-      <c r="C125" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D125" s="9" t="str">
+      <c r="C125" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D125" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3313,17 +3307,17 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="6">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" s="11">
         <v>39661</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="11">
         <v>39722</v>
       </c>
-      <c r="C126" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D126" s="9" t="str">
+      <c r="C126" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D126" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+2</v>
       </c>
@@ -3337,17 +3331,17 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="6">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127" s="11">
         <v>39692</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="11">
         <v>39752</v>
       </c>
-      <c r="C127" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D127" s="9" t="str">
+      <c r="C127" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D127" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -3361,17 +3355,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="6">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="11">
         <v>39722</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="11">
         <v>39780</v>
       </c>
-      <c r="C128" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D128" s="9" t="str">
+      <c r="C128" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D128" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -3385,17 +3379,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="6">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="11">
         <v>39753</v>
       </c>
-      <c r="B129" s="7">
+      <c r="B129" s="11">
         <v>39821</v>
       </c>
-      <c r="C129" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D129" s="9" t="str">
+      <c r="C129" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D129" s="5" t="str">
         <f t="shared" si="1"/>
         <v>UTC+1</v>
       </c>
@@ -3409,17 +3403,17 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="6">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="11">
         <v>39783</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="11">
         <v>39843</v>
       </c>
-      <c r="C130" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D130" s="9" t="str">
+      <c r="C130" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D130" s="5" t="str">
         <f t="shared" ref="D130:D193" si="2">IF(
  AND(
   B130 &gt;= EOMONTH(DATE(YEAR(B130),3,1),0)
@@ -3446,17 +3440,17 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="6">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="11">
         <v>39814</v>
       </c>
-      <c r="B131" s="7">
+      <c r="B131" s="11">
         <v>39871</v>
       </c>
-      <c r="C131" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D131" s="9" t="str">
+      <c r="C131" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D131" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -3470,17 +3464,17 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="6">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="11">
         <v>39845</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="11">
         <v>39904</v>
       </c>
-      <c r="C132" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D132" s="9" t="str">
+      <c r="C132" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D132" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3494,17 +3488,17 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="6">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="11">
         <v>39873</v>
       </c>
-      <c r="B133" s="7">
+      <c r="B133" s="11">
         <v>39933</v>
       </c>
-      <c r="C133" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D133" s="9" t="str">
+      <c r="C133" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D133" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3518,17 +3512,17 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="6">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="11">
         <v>39904</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="11">
         <v>39966</v>
       </c>
-      <c r="C134" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D134" s="9" t="str">
+      <c r="C134" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D134" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3542,17 +3536,17 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="6">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="11">
         <v>39934</v>
       </c>
-      <c r="B135" s="7">
+      <c r="B135" s="11">
         <v>39996</v>
       </c>
-      <c r="C135" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D135" s="9" t="str">
+      <c r="C135" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D135" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3566,17 +3560,17 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="6">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="11">
         <v>39965</v>
       </c>
-      <c r="B136" s="7">
+      <c r="B136" s="11">
         <v>40025</v>
       </c>
-      <c r="C136" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D136" s="9" t="str">
+      <c r="C136" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D136" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3590,17 +3584,17 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="6">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="11">
         <v>39995</v>
       </c>
-      <c r="B137" s="7">
+      <c r="B137" s="11">
         <v>40057</v>
       </c>
-      <c r="C137" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D137" s="9" t="str">
+      <c r="C137" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D137" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3614,17 +3608,17 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="6">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="11">
         <v>40026</v>
       </c>
-      <c r="B138" s="7">
+      <c r="B138" s="11">
         <v>40087</v>
       </c>
-      <c r="C138" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D138" s="9" t="str">
+      <c r="C138" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D138" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3638,17 +3632,17 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="6">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="11">
         <v>40057</v>
       </c>
-      <c r="B139" s="7">
+      <c r="B139" s="11">
         <v>40116</v>
       </c>
-      <c r="C139" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D139" s="9" t="str">
+      <c r="C139" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D139" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -3662,17 +3656,17 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="6">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="11">
         <v>40087</v>
       </c>
-      <c r="B140" s="7">
+      <c r="B140" s="11">
         <v>40148</v>
       </c>
-      <c r="C140" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D140" s="9" t="str">
+      <c r="C140" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D140" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -3686,17 +3680,17 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="6">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="11">
         <v>40118</v>
       </c>
-      <c r="B141" s="7">
+      <c r="B141" s="11">
         <v>40186</v>
       </c>
-      <c r="C141" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D141" s="9" t="str">
+      <c r="C141" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D141" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -3710,17 +3704,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="6">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="11">
         <v>40148</v>
       </c>
-      <c r="B142" s="7">
+      <c r="B142" s="11">
         <v>40207</v>
       </c>
-      <c r="C142" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D142" s="9" t="str">
+      <c r="C142" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D142" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -3734,17 +3728,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="6">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="11">
         <v>40179</v>
       </c>
-      <c r="B143" s="7">
+      <c r="B143" s="11">
         <v>40238</v>
       </c>
-      <c r="C143" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D143" s="9" t="str">
+      <c r="C143" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D143" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -3758,17 +3752,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="6">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="11">
         <v>40210</v>
       </c>
-      <c r="B144" s="7">
+      <c r="B144" s="11">
         <v>40268</v>
       </c>
-      <c r="C144" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D144" s="9" t="str">
+      <c r="C144" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D144" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3782,17 +3776,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="6">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="11">
         <v>40238</v>
       </c>
-      <c r="B145" s="7">
+      <c r="B145" s="11">
         <v>40298</v>
       </c>
-      <c r="C145" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D145" s="9" t="str">
+      <c r="C145" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D145" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3806,17 +3800,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="6">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="11">
         <v>40269</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="11">
         <v>40330</v>
       </c>
-      <c r="C146" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D146" s="9" t="str">
+      <c r="C146" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D146" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3830,17 +3824,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="6">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="11">
         <v>40299</v>
       </c>
-      <c r="B147" s="7">
+      <c r="B147" s="11">
         <v>40361</v>
       </c>
-      <c r="C147" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D147" s="9" t="str">
+      <c r="C147" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D147" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3854,17 +3848,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="6">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="11">
         <v>40330</v>
       </c>
-      <c r="B148" s="7">
+      <c r="B148" s="11">
         <v>40389</v>
       </c>
-      <c r="C148" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D148" s="9" t="str">
+      <c r="C148" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D148" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3878,17 +3872,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" s="6">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="11">
         <v>40360</v>
       </c>
-      <c r="B149" s="7">
+      <c r="B149" s="11">
         <v>40421</v>
       </c>
-      <c r="C149" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D149" s="9" t="str">
+      <c r="C149" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D149" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3902,17 +3896,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" s="6">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="11">
         <v>40391</v>
       </c>
-      <c r="B150" s="7">
+      <c r="B150" s="11">
         <v>40452</v>
       </c>
-      <c r="C150" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D150" s="9" t="str">
+      <c r="C150" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D150" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3926,17 +3920,17 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="6">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="11">
         <v>40422</v>
       </c>
-      <c r="B151" s="7">
+      <c r="B151" s="11">
         <v>40480</v>
       </c>
-      <c r="C151" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D151" s="9" t="str">
+      <c r="C151" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D151" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -3950,17 +3944,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="6">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" s="11">
         <v>40452</v>
       </c>
-      <c r="B152" s="7">
+      <c r="B152" s="11">
         <v>40512</v>
       </c>
-      <c r="C152" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D152" s="9" t="str">
+      <c r="C152" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D152" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -3974,17 +3968,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A153" s="6">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="11">
         <v>40483</v>
       </c>
-      <c r="B153" s="7">
+      <c r="B153" s="11">
         <v>40550</v>
       </c>
-      <c r="C153" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D153" s="9" t="str">
+      <c r="C153" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D153" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -3998,17 +3992,17 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A154" s="6">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" s="11">
         <v>40513</v>
       </c>
-      <c r="B154" s="7">
+      <c r="B154" s="11">
         <v>40575</v>
       </c>
-      <c r="C154" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D154" s="9" t="str">
+      <c r="C154" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D154" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4022,17 +4016,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="6">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="11">
         <v>40544</v>
       </c>
-      <c r="B155" s="7">
+      <c r="B155" s="11">
         <v>40603</v>
       </c>
-      <c r="C155" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D155" s="9" t="str">
+      <c r="C155" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D155" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4046,17 +4040,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="6">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" s="11">
         <v>40575</v>
       </c>
-      <c r="B156" s="7">
+      <c r="B156" s="11">
         <v>40634</v>
       </c>
-      <c r="C156" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D156" s="9" t="str">
+      <c r="C156" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D156" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4070,17 +4064,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="6">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="11">
         <v>40603</v>
       </c>
-      <c r="B157" s="7">
+      <c r="B157" s="11">
         <v>40662</v>
       </c>
-      <c r="C157" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D157" s="9" t="str">
+      <c r="C157" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D157" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4094,17 +4088,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="6">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="11">
         <v>40634</v>
       </c>
-      <c r="B158" s="7">
+      <c r="B158" s="11">
         <v>40694</v>
       </c>
-      <c r="C158" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D158" s="9" t="str">
+      <c r="C158" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D158" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4118,17 +4112,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" s="6">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" s="11">
         <v>40664</v>
       </c>
-      <c r="B159" s="7">
+      <c r="B159" s="11">
         <v>40725</v>
       </c>
-      <c r="C159" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D159" s="9" t="str">
+      <c r="C159" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D159" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4142,17 +4136,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" s="6">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" s="11">
         <v>40695</v>
       </c>
-      <c r="B160" s="7">
+      <c r="B160" s="11">
         <v>40756</v>
       </c>
-      <c r="C160" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D160" s="9" t="str">
+      <c r="C160" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D160" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4166,17 +4160,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A161" s="6">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="11">
         <v>40725</v>
       </c>
-      <c r="B161" s="7">
+      <c r="B161" s="11">
         <v>40786</v>
       </c>
-      <c r="C161" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D161" s="9" t="str">
+      <c r="C161" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D161" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4190,17 +4184,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A162" s="6">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="11">
         <v>40756</v>
       </c>
-      <c r="B162" s="7">
+      <c r="B162" s="11">
         <v>40816</v>
       </c>
-      <c r="C162" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D162" s="9" t="str">
+      <c r="C162" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D162" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4214,17 +4208,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A163" s="6">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" s="11">
         <v>40787</v>
       </c>
-      <c r="B163" s="7">
+      <c r="B163" s="11">
         <v>40847</v>
       </c>
-      <c r="C163" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D163" s="9" t="str">
+      <c r="C163" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D163" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4238,17 +4232,17 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A164" s="6">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" s="11">
         <v>40817</v>
       </c>
-      <c r="B164" s="7">
+      <c r="B164" s="11">
         <v>40877</v>
       </c>
-      <c r="C164" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D164" s="9" t="str">
+      <c r="C164" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D164" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4262,17 +4256,17 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" s="6">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165" s="11">
         <v>40848</v>
       </c>
-      <c r="B165" s="7">
+      <c r="B165" s="11">
         <v>40914</v>
       </c>
-      <c r="C165" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D165" s="9" t="str">
+      <c r="C165" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D165" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4286,17 +4280,17 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" s="6">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166" s="11">
         <v>40878</v>
       </c>
-      <c r="B166" s="7">
+      <c r="B166" s="11">
         <v>40939</v>
       </c>
-      <c r="C166" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D166" s="9" t="str">
+      <c r="C166" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D166" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4310,17 +4304,17 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A167" s="6">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A167" s="11">
         <v>40909</v>
       </c>
-      <c r="B167" s="7">
+      <c r="B167" s="11">
         <v>40969</v>
       </c>
-      <c r="C167" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D167" s="9" t="str">
+      <c r="C167" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D167" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4334,17 +4328,17 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" s="6">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A168" s="11">
         <v>40940</v>
       </c>
-      <c r="B168" s="7">
+      <c r="B168" s="11">
         <v>41001</v>
       </c>
-      <c r="C168" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D168" s="9" t="str">
+      <c r="C168" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D168" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4358,17 +4352,17 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A169" s="6">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A169" s="11">
         <v>40969</v>
       </c>
-      <c r="B169" s="7">
+      <c r="B169" s="11">
         <v>41031</v>
       </c>
-      <c r="C169" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D169" s="9" t="str">
+      <c r="C169" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D169" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4382,17 +4376,17 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A170" s="6">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="11">
         <v>41000</v>
       </c>
-      <c r="B170" s="7">
+      <c r="B170" s="11">
         <v>41061</v>
       </c>
-      <c r="C170" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D170" s="9" t="str">
+      <c r="C170" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D170" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4406,17 +4400,17 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A171" s="6">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="11">
         <v>41030</v>
       </c>
-      <c r="B171" s="7">
+      <c r="B171" s="11">
         <v>41092</v>
       </c>
-      <c r="C171" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D171" s="9" t="str">
+      <c r="C171" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D171" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4430,17 +4424,17 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A172" s="6">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="11">
         <v>41061</v>
       </c>
-      <c r="B172" s="7">
+      <c r="B172" s="11">
         <v>41121</v>
       </c>
-      <c r="C172" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D172" s="9" t="str">
+      <c r="C172" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D172" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4454,17 +4448,17 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" s="6">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="11">
         <v>41091</v>
       </c>
-      <c r="B173" s="7">
+      <c r="B173" s="11">
         <v>41152</v>
       </c>
-      <c r="C173" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D173" s="9" t="str">
+      <c r="C173" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D173" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4478,17 +4472,17 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" s="6">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="11">
         <v>41122</v>
       </c>
-      <c r="B174" s="7">
+      <c r="B174" s="11">
         <v>41183</v>
       </c>
-      <c r="C174" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D174" s="9" t="str">
+      <c r="C174" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D174" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4502,17 +4496,17 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" s="6">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="11">
         <v>41153</v>
       </c>
-      <c r="B175" s="7">
+      <c r="B175" s="11">
         <v>41213</v>
       </c>
-      <c r="C175" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D175" s="9" t="str">
+      <c r="C175" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D175" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4526,17 +4520,17 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A176" s="6">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="11">
         <v>41183</v>
       </c>
-      <c r="B176" s="7">
+      <c r="B176" s="11">
         <v>41243</v>
       </c>
-      <c r="C176" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D176" s="9" t="str">
+      <c r="C176" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D176" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4550,17 +4544,17 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" s="6">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="11">
         <v>41214</v>
       </c>
-      <c r="B177" s="7">
+      <c r="B177" s="11">
         <v>41282</v>
       </c>
-      <c r="C177" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D177" s="9" t="str">
+      <c r="C177" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D177" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4574,17 +4568,17 @@
         <v>0.11700000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="6">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="11">
         <v>41244</v>
       </c>
-      <c r="B178" s="7">
+      <c r="B178" s="11">
         <v>41306</v>
       </c>
-      <c r="C178" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D178" s="9" t="str">
+      <c r="C178" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D178" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4598,17 +4592,17 @@
         <v>0.11700000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" s="6">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="11">
         <v>41275</v>
       </c>
-      <c r="B179" s="7">
+      <c r="B179" s="11">
         <v>41334</v>
       </c>
-      <c r="C179" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D179" s="9" t="str">
+      <c r="C179" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D179" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4622,17 +4616,17 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" s="6">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180" s="11">
         <v>41306</v>
       </c>
-      <c r="B180" s="7">
+      <c r="B180" s="11">
         <v>41366</v>
       </c>
-      <c r="C180" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D180" s="9" t="str">
+      <c r="C180" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D180" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4646,17 +4640,17 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" s="6">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A181" s="11">
         <v>41334</v>
       </c>
-      <c r="B181" s="7">
+      <c r="B181" s="11">
         <v>41394</v>
       </c>
-      <c r="C181" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D181" s="9" t="str">
+      <c r="C181" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D181" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4670,17 +4664,17 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A182" s="6">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A182" s="11">
         <v>41365</v>
       </c>
-      <c r="B182" s="7">
+      <c r="B182" s="11">
         <v>41425</v>
       </c>
-      <c r="C182" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D182" s="9" t="str">
+      <c r="C182" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D182" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4694,17 +4688,17 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A183" s="6">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A183" s="11">
         <v>41395</v>
       </c>
-      <c r="B183" s="7">
+      <c r="B183" s="11">
         <v>41456</v>
       </c>
-      <c r="C183" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D183" s="9" t="str">
+      <c r="C183" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D183" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4718,17 +4712,17 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" s="6">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184" s="11">
         <v>41426</v>
       </c>
-      <c r="B184" s="7">
+      <c r="B184" s="11">
         <v>41486</v>
       </c>
-      <c r="C184" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D184" s="9" t="str">
+      <c r="C184" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D184" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4742,17 +4736,17 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A185" s="6">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A185" s="11">
         <v>41456</v>
       </c>
-      <c r="B185" s="7">
+      <c r="B185" s="11">
         <v>41516</v>
       </c>
-      <c r="C185" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D185" s="9" t="str">
+      <c r="C185" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D185" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4766,17 +4760,17 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" s="6">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A186" s="11">
         <v>41487</v>
       </c>
-      <c r="B186" s="7">
+      <c r="B186" s="11">
         <v>41548</v>
       </c>
-      <c r="C186" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D186" s="9" t="str">
+      <c r="C186" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D186" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4790,17 +4784,17 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" s="6">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A187" s="11">
         <v>41518</v>
       </c>
-      <c r="B187" s="7">
+      <c r="B187" s="11">
         <v>41578</v>
       </c>
-      <c r="C187" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D187" s="9" t="str">
+      <c r="C187" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D187" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4814,17 +4808,17 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" s="6">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A188" s="11">
         <v>41548</v>
       </c>
-      <c r="B188" s="7">
+      <c r="B188" s="11">
         <v>41607</v>
       </c>
-      <c r="C188" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D188" s="9" t="str">
+      <c r="C188" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D188" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4838,17 +4832,17 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" s="6">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A189" s="11">
         <v>41579</v>
       </c>
-      <c r="B189" s="7">
+      <c r="B189" s="11">
         <v>41647</v>
       </c>
-      <c r="C189" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D189" s="9" t="str">
+      <c r="C189" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D189" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4862,17 +4856,17 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" s="6">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A190" s="11">
         <v>41609</v>
       </c>
-      <c r="B190" s="7">
+      <c r="B190" s="11">
         <v>41670</v>
       </c>
-      <c r="C190" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D190" s="9" t="str">
+      <c r="C190" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D190" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4886,17 +4880,17 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A191" s="6">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A191" s="11">
         <v>41640</v>
       </c>
-      <c r="B191" s="7">
+      <c r="B191" s="11">
         <v>41698</v>
       </c>
-      <c r="C191" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D191" s="9" t="str">
+      <c r="C191" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D191" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+1</v>
       </c>
@@ -4910,17 +4904,17 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" s="6">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A192" s="11">
         <v>41671</v>
       </c>
-      <c r="B192" s="7">
+      <c r="B192" s="11">
         <v>41730</v>
       </c>
-      <c r="C192" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D192" s="9" t="str">
+      <c r="C192" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D192" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4934,17 +4928,17 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A193" s="6">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A193" s="11">
         <v>41699</v>
       </c>
-      <c r="B193" s="7">
+      <c r="B193" s="11">
         <v>41761</v>
       </c>
-      <c r="C193" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D193" s="9" t="str">
+      <c r="C193" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D193" s="5" t="str">
         <f t="shared" si="2"/>
         <v>UTC+2</v>
       </c>
@@ -4958,17 +4952,17 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A194" s="6">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A194" s="11">
         <v>41730</v>
       </c>
-      <c r="B194" s="7">
+      <c r="B194" s="11">
         <v>41793</v>
       </c>
-      <c r="C194" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D194" s="9" t="str">
+      <c r="C194" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D194" s="5" t="str">
         <f t="shared" ref="D194:D257" si="3">IF(
  AND(
   B194 &gt;= EOMONTH(DATE(YEAR(B194),3,1),0)
@@ -4995,17 +4989,17 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A195" s="6">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A195" s="11">
         <v>41760</v>
       </c>
-      <c r="B195" s="7">
+      <c r="B195" s="11">
         <v>41821</v>
       </c>
-      <c r="C195" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D195" s="9" t="str">
+      <c r="C195" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D195" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5019,17 +5013,17 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A196" s="6">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A196" s="11">
         <v>41791</v>
       </c>
-      <c r="B196" s="7">
+      <c r="B196" s="11">
         <v>41851</v>
       </c>
-      <c r="C196" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D196" s="9" t="str">
+      <c r="C196" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D196" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5043,17 +5037,17 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" s="6">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197" s="11">
         <v>41821</v>
       </c>
-      <c r="B197" s="7">
+      <c r="B197" s="11">
         <v>41880</v>
       </c>
-      <c r="C197" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D197" s="9" t="str">
+      <c r="C197" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D197" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5067,17 +5061,17 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" s="6">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198" s="11">
         <v>41852</v>
       </c>
-      <c r="B198" s="7">
+      <c r="B198" s="11">
         <v>41912</v>
       </c>
-      <c r="C198" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D198" s="9" t="str">
+      <c r="C198" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D198" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5091,17 +5085,17 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A199" s="6">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A199" s="11">
         <v>41883</v>
       </c>
-      <c r="B199" s="7">
+      <c r="B199" s="11">
         <v>41943</v>
       </c>
-      <c r="C199" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D199" s="9" t="str">
+      <c r="C199" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D199" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5115,17 +5109,17 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A200" s="6">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A200" s="11">
         <v>41913</v>
       </c>
-      <c r="B200" s="7">
+      <c r="B200" s="11">
         <v>41971</v>
       </c>
-      <c r="C200" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D200" s="9" t="str">
+      <c r="C200" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D200" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5139,17 +5133,17 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A201" s="6">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A201" s="11">
         <v>41944</v>
       </c>
-      <c r="B201" s="7">
+      <c r="B201" s="11">
         <v>42011</v>
       </c>
-      <c r="C201" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D201" s="9" t="str">
+      <c r="C201" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D201" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5163,17 +5157,17 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A202" s="6">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A202" s="11">
         <v>41974</v>
       </c>
-      <c r="B202" s="7">
+      <c r="B202" s="11">
         <v>42034</v>
       </c>
-      <c r="C202" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D202" s="9" t="str">
+      <c r="C202" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D202" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5187,17 +5181,17 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A203" s="6">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A203" s="11">
         <v>42005</v>
       </c>
-      <c r="B203" s="7">
+      <c r="B203" s="11">
         <v>42065</v>
       </c>
-      <c r="C203" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D203" s="9" t="str">
+      <c r="C203" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D203" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5211,17 +5205,17 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A204" s="6">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A204" s="11">
         <v>42036</v>
       </c>
-      <c r="B204" s="7">
+      <c r="B204" s="11">
         <v>42094</v>
       </c>
-      <c r="C204" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D204" s="9" t="str">
+      <c r="C204" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D204" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5235,17 +5229,17 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A205" s="6">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A205" s="11">
         <v>42064</v>
       </c>
-      <c r="B205" s="7">
+      <c r="B205" s="11">
         <v>42124</v>
       </c>
-      <c r="C205" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D205" s="9" t="str">
+      <c r="C205" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D205" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5259,17 +5253,17 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A206" s="6">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A206" s="11">
         <v>42095</v>
       </c>
-      <c r="B206" s="7">
+      <c r="B206" s="11">
         <v>42158</v>
       </c>
-      <c r="C206" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D206" s="9" t="str">
+      <c r="C206" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D206" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5283,17 +5277,17 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A207" s="6">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A207" s="11">
         <v>42125</v>
       </c>
-      <c r="B207" s="7">
+      <c r="B207" s="11">
         <v>42185</v>
       </c>
-      <c r="C207" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D207" s="9" t="str">
+      <c r="C207" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D207" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5307,17 +5301,17 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A208" s="6">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A208" s="11">
         <v>42156</v>
       </c>
-      <c r="B208" s="7">
+      <c r="B208" s="11">
         <v>42216</v>
       </c>
-      <c r="C208" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D208" s="9" t="str">
+      <c r="C208" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D208" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5331,17 +5325,17 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A209" s="6">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A209" s="11">
         <v>42186</v>
       </c>
-      <c r="B209" s="7">
+      <c r="B209" s="11">
         <v>42248</v>
       </c>
-      <c r="C209" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D209" s="9" t="str">
+      <c r="C209" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D209" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5355,17 +5349,17 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A210" s="6">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A210" s="11">
         <v>42217</v>
       </c>
-      <c r="B210" s="7">
+      <c r="B210" s="11">
         <v>42277</v>
       </c>
-      <c r="C210" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D210" s="9" t="str">
+      <c r="C210" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D210" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5379,17 +5373,17 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A211" s="6">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A211" s="11">
         <v>42248</v>
       </c>
-      <c r="B211" s="7">
+      <c r="B211" s="11">
         <v>42307</v>
       </c>
-      <c r="C211" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D211" s="9" t="str">
+      <c r="C211" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D211" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5403,17 +5397,17 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A212" s="6">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A212" s="11">
         <v>42278</v>
       </c>
-      <c r="B212" s="7">
+      <c r="B212" s="11">
         <v>42339</v>
       </c>
-      <c r="C212" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D212" s="9" t="str">
+      <c r="C212" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D212" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5427,17 +5421,17 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A213" s="6">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A213" s="11">
         <v>42309</v>
       </c>
-      <c r="B213" s="7">
+      <c r="B213" s="11">
         <v>42376</v>
       </c>
-      <c r="C213" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D213" s="9" t="str">
+      <c r="C213" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D213" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5451,17 +5445,17 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A214" s="6">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A214" s="11">
         <v>42339</v>
       </c>
-      <c r="B214" s="7">
+      <c r="B214" s="11">
         <v>42402</v>
       </c>
-      <c r="C214" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D214" s="9" t="str">
+      <c r="C214" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D214" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5475,17 +5469,17 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A215" s="6">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A215" s="11">
         <v>42370</v>
       </c>
-      <c r="B215" s="7">
+      <c r="B215" s="11">
         <v>42430</v>
       </c>
-      <c r="C215" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D215" s="9" t="str">
+      <c r="C215" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D215" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5499,17 +5493,17 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A216" s="6">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A216" s="11">
         <v>42401</v>
       </c>
-      <c r="B216" s="7">
+      <c r="B216" s="11">
         <v>42464</v>
       </c>
-      <c r="C216" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D216" s="9" t="str">
+      <c r="C216" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D216" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5523,17 +5517,17 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A217" s="6">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A217" s="11">
         <v>42430</v>
       </c>
-      <c r="B217" s="7">
+      <c r="B217" s="11">
         <v>42489</v>
       </c>
-      <c r="C217" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D217" s="9" t="str">
+      <c r="C217" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D217" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5547,17 +5541,17 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A218" s="6">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A218" s="11">
         <v>42461</v>
       </c>
-      <c r="B218" s="7">
+      <c r="B218" s="11">
         <v>42521</v>
       </c>
-      <c r="C218" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D218" s="9" t="str">
+      <c r="C218" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D218" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5571,17 +5565,17 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A219" s="6">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A219" s="11">
         <v>42491</v>
       </c>
-      <c r="B219" s="7">
+      <c r="B219" s="11">
         <v>42552</v>
       </c>
-      <c r="C219" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D219" s="9" t="str">
+      <c r="C219" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D219" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5595,17 +5589,17 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A220" s="6">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A220" s="11">
         <v>42522</v>
       </c>
-      <c r="B220" s="7">
+      <c r="B220" s="11">
         <v>42580</v>
       </c>
-      <c r="C220" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D220" s="9" t="str">
+      <c r="C220" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D220" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5619,17 +5613,17 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A221" s="6">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A221" s="11">
         <v>42552</v>
       </c>
-      <c r="B221" s="7">
+      <c r="B221" s="11">
         <v>42613</v>
       </c>
-      <c r="C221" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D221" s="9" t="str">
+      <c r="C221" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D221" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5643,17 +5637,17 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A222" s="6">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A222" s="11">
         <v>42583</v>
       </c>
-      <c r="B222" s="7">
+      <c r="B222" s="11">
         <v>42643</v>
       </c>
-      <c r="C222" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D222" s="9" t="str">
+      <c r="C222" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D222" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5667,17 +5661,17 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A223" s="6">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A223" s="11">
         <v>42614</v>
       </c>
-      <c r="B223" s="7">
+      <c r="B223" s="11">
         <v>42677</v>
       </c>
-      <c r="C223" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D223" s="9" t="str">
+      <c r="C223" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D223" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5691,17 +5685,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A224" s="6">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A224" s="11">
         <v>42644</v>
       </c>
-      <c r="B224" s="7">
+      <c r="B224" s="11">
         <v>42705</v>
       </c>
-      <c r="C224" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D224" s="9" t="str">
+      <c r="C224" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D224" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5715,17 +5709,17 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A225" s="6">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A225" s="11">
         <v>42675</v>
       </c>
-      <c r="B225" s="7">
+      <c r="B225" s="11">
         <v>42744</v>
       </c>
-      <c r="C225" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D225" s="9" t="str">
+      <c r="C225" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D225" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5739,17 +5733,17 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A226" s="6">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A226" s="11">
         <v>42705</v>
       </c>
-      <c r="B226" s="7">
+      <c r="B226" s="11">
         <v>42766</v>
       </c>
-      <c r="C226" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D226" s="9" t="str">
+      <c r="C226" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D226" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5763,17 +5757,17 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A227" s="6">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A227" s="11">
         <v>42736</v>
       </c>
-      <c r="B227" s="7">
+      <c r="B227" s="11">
         <v>42796</v>
       </c>
-      <c r="C227" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D227" s="9" t="str">
+      <c r="C227" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D227" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5787,17 +5781,17 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A228" s="6">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A228" s="11">
         <v>42767</v>
       </c>
-      <c r="B228" s="7">
+      <c r="B228" s="11">
         <v>42828</v>
       </c>
-      <c r="C228" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D228" s="9" t="str">
+      <c r="C228" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D228" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5811,17 +5805,17 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A229" s="6">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A229" s="11">
         <v>42795</v>
       </c>
-      <c r="B229" s="7">
+      <c r="B229" s="11">
         <v>42857</v>
       </c>
-      <c r="C229" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D229" s="9" t="str">
+      <c r="C229" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D229" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5835,17 +5829,17 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A230" s="6">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A230" s="11">
         <v>42826</v>
       </c>
-      <c r="B230" s="7">
+      <c r="B230" s="11">
         <v>42886</v>
       </c>
-      <c r="C230" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D230" s="9" t="str">
+      <c r="C230" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D230" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5859,17 +5853,17 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A231" s="6">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A231" s="11">
         <v>42856</v>
       </c>
-      <c r="B231" s="7">
+      <c r="B231" s="11">
         <v>42919</v>
       </c>
-      <c r="C231" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D231" s="9" t="str">
+      <c r="C231" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D231" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5883,17 +5877,17 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A232" s="6">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A232" s="11">
         <v>42887</v>
       </c>
-      <c r="B232" s="7">
+      <c r="B232" s="11">
         <v>42947</v>
       </c>
-      <c r="C232" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D232" s="9" t="str">
+      <c r="C232" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D232" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5907,17 +5901,17 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A233" s="6">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A233" s="11">
         <v>42917</v>
       </c>
-      <c r="B233" s="7">
+      <c r="B233" s="11">
         <v>42978</v>
       </c>
-      <c r="C233" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D233" s="9" t="str">
+      <c r="C233" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D233" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5931,17 +5925,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A234" s="6">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A234" s="11">
         <v>42948</v>
       </c>
-      <c r="B234" s="7">
+      <c r="B234" s="11">
         <v>43010</v>
       </c>
-      <c r="C234" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D234" s="9" t="str">
+      <c r="C234" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D234" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -5955,17 +5949,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A235" s="6">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A235" s="11">
         <v>42979</v>
       </c>
-      <c r="B235" s="7">
+      <c r="B235" s="11">
         <v>43039</v>
       </c>
-      <c r="C235" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D235" s="9" t="str">
+      <c r="C235" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D235" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -5979,17 +5973,17 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A236" s="6">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A236" s="11">
         <v>43009</v>
       </c>
-      <c r="B236" s="7">
+      <c r="B236" s="11">
         <v>43069</v>
       </c>
-      <c r="C236" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D236" s="9" t="str">
+      <c r="C236" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D236" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -6003,17 +5997,17 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A237" s="6">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A237" s="11">
         <v>43040</v>
       </c>
-      <c r="B237" s="7">
+      <c r="B237" s="11">
         <v>43109</v>
       </c>
-      <c r="C237" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D237" s="9" t="str">
+      <c r="C237" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D237" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -6027,17 +6021,17 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A238" s="6">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A238" s="11">
         <v>43070</v>
       </c>
-      <c r="B238" s="7">
+      <c r="B238" s="11">
         <v>43131</v>
       </c>
-      <c r="C238" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D238" s="9" t="str">
+      <c r="C238" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D238" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -6051,17 +6045,17 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A239" s="6">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A239" s="11">
         <v>43101</v>
       </c>
-      <c r="B239" s="7">
+      <c r="B239" s="11">
         <v>43160</v>
       </c>
-      <c r="C239" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D239" s="9" t="str">
+      <c r="C239" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D239" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -6075,17 +6069,17 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A240" s="6">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A240" s="11">
         <v>43132</v>
       </c>
-      <c r="B240" s="7">
+      <c r="B240" s="11">
         <v>43194</v>
       </c>
-      <c r="C240" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D240" s="9" t="str">
+      <c r="C240" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D240" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6099,17 +6093,17 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A241" s="6">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A241" s="11">
         <v>43160</v>
       </c>
-      <c r="B241" s="7">
+      <c r="B241" s="11">
         <v>43222</v>
       </c>
-      <c r="C241" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D241" s="9" t="str">
+      <c r="C241" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D241" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6123,17 +6117,17 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A242" s="6">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A242" s="11">
         <v>43191</v>
       </c>
-      <c r="B242" s="7">
+      <c r="B242" s="11">
         <v>43251</v>
       </c>
-      <c r="C242" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D242" s="9" t="str">
+      <c r="C242" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D242" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6147,17 +6141,17 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A243" s="6">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A243" s="11">
         <v>43221</v>
       </c>
-      <c r="B243" s="7">
+      <c r="B243" s="11">
         <v>43283</v>
       </c>
-      <c r="C243" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D243" s="9" t="str">
+      <c r="C243" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D243" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6171,17 +6165,17 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A244" s="6">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A244" s="11">
         <v>43252</v>
       </c>
-      <c r="B244" s="7">
+      <c r="B244" s="11">
         <v>43312</v>
       </c>
-      <c r="C244" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D244" s="9" t="str">
+      <c r="C244" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D244" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6195,17 +6189,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A245" s="6">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A245" s="11">
         <v>43282</v>
       </c>
-      <c r="B245" s="7">
+      <c r="B245" s="11">
         <v>43343</v>
       </c>
-      <c r="C245" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D245" s="9" t="str">
+      <c r="C245" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D245" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6219,17 +6213,17 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A246" s="6">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A246" s="11">
         <v>43313</v>
       </c>
-      <c r="B246" s="7">
+      <c r="B246" s="11">
         <v>43374</v>
       </c>
-      <c r="C246" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D246" s="9" t="str">
+      <c r="C246" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D246" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6243,17 +6237,17 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A247" s="6">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A247" s="11">
         <v>43344</v>
       </c>
-      <c r="B247" s="7">
+      <c r="B247" s="11">
         <v>43404</v>
       </c>
-      <c r="C247" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D247" s="9" t="str">
+      <c r="C247" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D247" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -6267,17 +6261,17 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A248" s="6">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A248" s="11">
         <v>43374</v>
       </c>
-      <c r="B248" s="7">
+      <c r="B248" s="11">
         <v>43434</v>
       </c>
-      <c r="C248" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D248" s="9" t="str">
+      <c r="C248" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D248" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -6291,17 +6285,17 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" s="6">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A249" s="11">
         <v>43405</v>
       </c>
-      <c r="B249" s="7">
+      <c r="B249" s="11">
         <v>43474</v>
       </c>
-      <c r="C249" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D249" s="9" t="str">
+      <c r="C249" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D249" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -6315,17 +6309,17 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" s="6">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A250" s="11">
         <v>43435</v>
       </c>
-      <c r="B250" s="7">
+      <c r="B250" s="11">
         <v>43496</v>
       </c>
-      <c r="C250" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D250" s="9" t="str">
+      <c r="C250" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D250" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -6339,17 +6333,17 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A251" s="6">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A251" s="11">
         <v>43466</v>
       </c>
-      <c r="B251" s="7">
+      <c r="B251" s="11">
         <v>43525</v>
       </c>
-      <c r="C251" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D251" s="9" t="str">
+      <c r="C251" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D251" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+1</v>
       </c>
@@ -6363,17 +6357,17 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A252" s="6">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A252" s="11">
         <v>43497</v>
       </c>
-      <c r="B252" s="7">
+      <c r="B252" s="11">
         <v>43556</v>
       </c>
-      <c r="C252" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D252" s="9" t="str">
+      <c r="C252" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D252" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6387,17 +6381,17 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A253" s="6">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A253" s="11">
         <v>43525</v>
       </c>
-      <c r="B253" s="7">
+      <c r="B253" s="11">
         <v>43585</v>
       </c>
-      <c r="C253" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D253" s="9" t="str">
+      <c r="C253" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D253" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6411,17 +6405,17 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A254" s="6">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A254" s="11">
         <v>43556</v>
       </c>
-      <c r="B254" s="7">
+      <c r="B254" s="11">
         <v>43620</v>
       </c>
-      <c r="C254" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D254" s="9" t="str">
+      <c r="C254" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D254" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6435,17 +6429,17 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A255" s="6">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A255" s="11">
         <v>43586</v>
       </c>
-      <c r="B255" s="7">
+      <c r="B255" s="11">
         <v>43647</v>
       </c>
-      <c r="C255" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D255" s="9" t="str">
+      <c r="C255" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D255" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6459,17 +6453,17 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A256" s="6">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A256" s="11">
         <v>43617</v>
       </c>
-      <c r="B256" s="7">
+      <c r="B256" s="11">
         <v>43677</v>
       </c>
-      <c r="C256" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D256" s="9" t="str">
+      <c r="C256" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D256" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6483,17 +6477,17 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A257" s="6">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A257" s="11">
         <v>43647</v>
       </c>
-      <c r="B257" s="7">
+      <c r="B257" s="11">
         <v>43707</v>
       </c>
-      <c r="C257" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D257" s="9" t="str">
+      <c r="C257" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D257" s="5" t="str">
         <f t="shared" si="3"/>
         <v>UTC+2</v>
       </c>
@@ -6507,17 +6501,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A258" s="6">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A258" s="11">
         <v>43678</v>
       </c>
-      <c r="B258" s="7">
+      <c r="B258" s="11">
         <v>43738</v>
       </c>
-      <c r="C258" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D258" s="9" t="str">
+      <c r="C258" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D258" s="5" t="str">
         <f t="shared" ref="D258:D321" si="4">IF(
  AND(
   B258 &gt;= EOMONTH(DATE(YEAR(B258),3,1),0)
@@ -6544,17 +6538,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A259" s="6">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A259" s="11">
         <v>43709</v>
       </c>
-      <c r="B259" s="7">
+      <c r="B259" s="11">
         <v>43769</v>
       </c>
-      <c r="C259" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D259" s="9" t="str">
+      <c r="C259" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D259" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6568,17 +6562,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A260" s="6">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A260" s="11">
         <v>43739</v>
       </c>
-      <c r="B260" s="7">
+      <c r="B260" s="11">
         <v>43798</v>
       </c>
-      <c r="C260" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D260" s="9" t="str">
+      <c r="C260" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D260" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6592,17 +6586,17 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A261" s="6">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A261" s="11">
         <v>43770</v>
       </c>
-      <c r="B261" s="7">
+      <c r="B261" s="11">
         <v>43839</v>
       </c>
-      <c r="C261" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D261" s="9" t="str">
+      <c r="C261" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D261" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6616,17 +6610,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A262" s="6">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A262" s="11">
         <v>43800</v>
       </c>
-      <c r="B262" s="7">
+      <c r="B262" s="11">
         <v>43860</v>
       </c>
-      <c r="C262" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D262" s="9" t="str">
+      <c r="C262" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D262" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6640,17 +6634,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A263" s="6">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A263" s="11">
         <v>43831</v>
       </c>
-      <c r="B263" s="7">
+      <c r="B263" s="11">
         <v>43893</v>
       </c>
-      <c r="C263" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D263" s="9" t="str">
+      <c r="C263" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D263" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6664,17 +6658,17 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A264" s="6">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A264" s="11">
         <v>43862</v>
       </c>
-      <c r="B264" s="7">
+      <c r="B264" s="11">
         <v>43922</v>
       </c>
-      <c r="C264" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D264" s="9" t="str">
+      <c r="C264" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D264" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -6688,17 +6682,17 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A265" s="6">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A265" s="11">
         <v>43891</v>
       </c>
-      <c r="B265" s="7">
+      <c r="B265" s="11">
         <v>43951</v>
       </c>
-      <c r="C265" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D265" s="9" t="str">
+      <c r="C265" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D265" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -6712,17 +6706,17 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A266" s="6">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A266" s="11">
         <v>43922</v>
       </c>
-      <c r="B266" s="7">
+      <c r="B266" s="11">
         <v>43985</v>
       </c>
-      <c r="C266" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D266" s="9" t="str">
+      <c r="C266" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D266" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -6736,17 +6730,17 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A267" s="6">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A267" s="11">
         <v>43952</v>
       </c>
-      <c r="B267" s="7">
+      <c r="B267" s="11">
         <v>44014</v>
       </c>
-      <c r="C267" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D267" s="9" t="str">
+      <c r="C267" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D267" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -6760,17 +6754,17 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A268" s="6">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A268" s="11">
         <v>43983</v>
       </c>
-      <c r="B268" s="7">
+      <c r="B268" s="11">
         <v>44042</v>
       </c>
-      <c r="C268" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D268" s="9" t="str">
+      <c r="C268" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D268" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -6784,17 +6778,17 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A269" s="6">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A269" s="11">
         <v>44013</v>
       </c>
-      <c r="B269" s="7">
+      <c r="B269" s="11">
         <v>44075</v>
       </c>
-      <c r="C269" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D269" s="9" t="str">
+      <c r="C269" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D269" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -6808,17 +6802,17 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A270" s="6">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A270" s="11">
         <v>44044</v>
       </c>
-      <c r="B270" s="7">
+      <c r="B270" s="11">
         <v>44105</v>
       </c>
-      <c r="C270" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D270" s="9" t="str">
+      <c r="C270" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D270" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -6832,17 +6826,17 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A271" s="6">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A271" s="11">
         <v>44075</v>
       </c>
-      <c r="B271" s="7">
+      <c r="B271" s="11">
         <v>44134</v>
       </c>
-      <c r="C271" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D271" s="9" t="str">
+      <c r="C271" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D271" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6856,17 +6850,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A272" s="6">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A272" s="11">
         <v>44105</v>
       </c>
-      <c r="B272" s="7">
+      <c r="B272" s="11">
         <v>44167</v>
       </c>
-      <c r="C272" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D272" s="9" t="str">
+      <c r="C272" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D272" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6880,17 +6874,17 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A273" s="6">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A273" s="11">
         <v>44136</v>
       </c>
-      <c r="B273" s="7">
+      <c r="B273" s="11">
         <v>44204</v>
       </c>
-      <c r="C273" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D273" s="9" t="str">
+      <c r="C273" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D273" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6904,17 +6898,17 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A274" s="6">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274" s="11">
         <v>44166</v>
       </c>
-      <c r="B274" s="7">
+      <c r="B274" s="11">
         <v>44228</v>
       </c>
-      <c r="C274" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D274" s="9" t="str">
+      <c r="C274" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D274" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6928,17 +6922,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A275" s="6">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A275" s="11">
         <v>44197</v>
       </c>
-      <c r="B275" s="7">
+      <c r="B275" s="11">
         <v>44259</v>
       </c>
-      <c r="C275" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D275" s="9" t="str">
+      <c r="C275" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D275" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -6952,17 +6946,17 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A276" s="6">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A276" s="11">
         <v>44228</v>
       </c>
-      <c r="B276" s="7">
+      <c r="B276" s="11">
         <v>44292</v>
       </c>
-      <c r="C276" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D276" s="9" t="str">
+      <c r="C276" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D276" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -6976,17 +6970,17 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A277" s="6">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A277" s="11">
         <v>44256</v>
       </c>
-      <c r="B277" s="7">
+      <c r="B277" s="11">
         <v>44316</v>
       </c>
-      <c r="C277" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D277" s="9" t="str">
+      <c r="C277" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D277" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7000,17 +6994,17 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A278" s="6">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A278" s="11">
         <v>44287</v>
       </c>
-      <c r="B278" s="7">
+      <c r="B278" s="11">
         <v>44348</v>
       </c>
-      <c r="C278" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D278" s="9" t="str">
+      <c r="C278" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D278" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7024,17 +7018,17 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A279" s="6">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A279" s="11">
         <v>44317</v>
       </c>
-      <c r="B279" s="7">
+      <c r="B279" s="11">
         <v>44378</v>
       </c>
-      <c r="C279" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D279" s="9" t="str">
+      <c r="C279" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D279" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7048,17 +7042,17 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A280" s="6">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A280" s="11">
         <v>44348</v>
       </c>
-      <c r="B280" s="7">
+      <c r="B280" s="11">
         <v>44407</v>
       </c>
-      <c r="C280" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D280" s="9" t="str">
+      <c r="C280" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D280" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7072,17 +7066,17 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A281" s="6">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A281" s="11">
         <v>44378</v>
       </c>
-      <c r="B281" s="7">
+      <c r="B281" s="11">
         <v>44440</v>
       </c>
-      <c r="C281" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D281" s="9" t="str">
+      <c r="C281" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D281" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7096,17 +7090,17 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A282" s="6">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A282" s="11">
         <v>44409</v>
       </c>
-      <c r="B282" s="7">
+      <c r="B282" s="11">
         <v>44469</v>
       </c>
-      <c r="C282" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D282" s="9" t="str">
+      <c r="C282" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D282" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7120,17 +7114,17 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A283" s="6">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A283" s="11">
         <v>44440</v>
       </c>
-      <c r="B283" s="7">
+      <c r="B283" s="11">
         <v>44503</v>
       </c>
-      <c r="C283" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D283" s="9" t="str">
+      <c r="C283" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D283" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7144,17 +7138,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A284" s="6">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A284" s="11">
         <v>44470</v>
       </c>
-      <c r="B284" s="7">
+      <c r="B284" s="11">
         <v>44532</v>
       </c>
-      <c r="C284" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D284" s="9" t="str">
+      <c r="C284" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D284" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7168,17 +7162,17 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A285" s="6">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A285" s="11">
         <v>44501</v>
       </c>
-      <c r="B285" s="7">
+      <c r="B285" s="11">
         <v>44571</v>
       </c>
-      <c r="C285" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D285" s="9" t="str">
+      <c r="C285" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D285" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7192,17 +7186,17 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A286" s="6">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A286" s="11">
         <v>44531</v>
       </c>
-      <c r="B286" s="7">
+      <c r="B286" s="11">
         <v>44593</v>
       </c>
-      <c r="C286" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D286" s="9" t="str">
+      <c r="C286" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D286" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7216,17 +7210,17 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A287" s="6">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A287" s="11">
         <v>44562</v>
       </c>
-      <c r="B287" s="7">
+      <c r="B287" s="11">
         <v>44623</v>
       </c>
-      <c r="C287" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D287" s="9" t="str">
+      <c r="C287" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D287" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7240,17 +7234,17 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A288" s="6">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A288" s="11">
         <v>44593</v>
       </c>
-      <c r="B288" s="7">
+      <c r="B288" s="11">
         <v>44651</v>
       </c>
-      <c r="C288" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D288" s="9" t="str">
+      <c r="C288" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D288" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7264,17 +7258,17 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A289" s="6">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A289" s="11">
         <v>44621</v>
       </c>
-      <c r="B289" s="7">
+      <c r="B289" s="11">
         <v>44684</v>
       </c>
-      <c r="C289" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D289" s="9" t="str">
+      <c r="C289" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D289" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7288,17 +7282,17 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A290" s="6">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A290" s="11">
         <v>44652</v>
       </c>
-      <c r="B290" s="7">
+      <c r="B290" s="11">
         <v>44713</v>
       </c>
-      <c r="C290" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D290" s="9" t="str">
+      <c r="C290" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D290" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7312,17 +7306,17 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A291" s="6">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A291" s="11">
         <v>44682</v>
       </c>
-      <c r="B291" s="7">
+      <c r="B291" s="11">
         <v>44742</v>
       </c>
-      <c r="C291" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D291" s="9" t="str">
+      <c r="C291" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D291" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7336,17 +7330,17 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A292" s="6">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A292" s="11">
         <v>44713</v>
       </c>
-      <c r="B292" s="7">
+      <c r="B292" s="11">
         <v>44774</v>
       </c>
-      <c r="C292" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D292" s="9" t="str">
+      <c r="C292" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D292" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7360,17 +7354,17 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A293" s="6">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A293" s="11">
         <v>44743</v>
       </c>
-      <c r="B293" s="7">
+      <c r="B293" s="11">
         <v>44805</v>
       </c>
-      <c r="C293" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D293" s="9" t="str">
+      <c r="C293" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D293" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7384,17 +7378,17 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" s="6">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A294" s="11">
         <v>44774</v>
       </c>
-      <c r="B294" s="7">
+      <c r="B294" s="11">
         <v>44834</v>
       </c>
-      <c r="C294" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D294" s="9" t="str">
+      <c r="C294" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D294" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7408,17 +7402,17 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A295" s="6">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A295" s="11">
         <v>44805</v>
       </c>
-      <c r="B295" s="7">
+      <c r="B295" s="11">
         <v>44868</v>
       </c>
-      <c r="C295" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D295" s="9" t="str">
+      <c r="C295" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D295" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7432,17 +7426,17 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A296" s="6">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A296" s="11">
         <v>44835</v>
       </c>
-      <c r="B296" s="7">
+      <c r="B296" s="11">
         <v>44896</v>
       </c>
-      <c r="C296" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D296" s="9" t="str">
+      <c r="C296" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D296" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7456,17 +7450,17 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A297" s="6">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A297" s="11">
         <v>44866</v>
       </c>
-      <c r="B297" s="7">
+      <c r="B297" s="11">
         <v>44935</v>
       </c>
-      <c r="C297" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D297" s="9" t="str">
+      <c r="C297" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D297" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7480,17 +7474,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A298" s="6">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A298" s="11">
         <v>44896</v>
       </c>
-      <c r="B298" s="7">
+      <c r="B298" s="11">
         <v>44958</v>
       </c>
-      <c r="C298" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D298" s="9" t="str">
+      <c r="C298" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D298" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7504,17 +7498,17 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A299" s="6">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A299" s="11">
         <v>44927</v>
       </c>
-      <c r="B299" s="7">
+      <c r="B299" s="11">
         <v>44987</v>
       </c>
-      <c r="C299" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D299" s="9" t="str">
+      <c r="C299" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D299" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7528,17 +7522,17 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A300" s="6">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A300" s="11">
         <v>44958</v>
       </c>
-      <c r="B300" s="7">
+      <c r="B300" s="11">
         <v>45016</v>
       </c>
-      <c r="C300" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D300" s="9" t="str">
+      <c r="C300" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D300" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7552,17 +7546,17 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A301" s="6">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A301" s="11">
         <v>44986</v>
       </c>
-      <c r="B301" s="7">
+      <c r="B301" s="11">
         <v>45049</v>
       </c>
-      <c r="C301" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D301" s="9" t="str">
+      <c r="C301" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D301" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7576,17 +7570,17 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A302" s="6">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A302" s="11">
         <v>45017</v>
       </c>
-      <c r="B302" s="7">
+      <c r="B302" s="11">
         <v>45078</v>
       </c>
-      <c r="C302" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D302" s="9" t="str">
+      <c r="C302" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D302" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7600,17 +7594,17 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A303" s="6">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A303" s="11">
         <v>45047</v>
       </c>
-      <c r="B303" s="7">
+      <c r="B303" s="11">
         <v>45107</v>
       </c>
-      <c r="C303" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D303" s="9" t="str">
+      <c r="C303" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D303" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7624,17 +7618,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A304" s="6">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A304" s="11">
         <v>45078</v>
       </c>
-      <c r="B304" s="7">
+      <c r="B304" s="11">
         <v>45139</v>
       </c>
-      <c r="C304" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D304" s="9" t="str">
+      <c r="C304" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D304" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7648,17 +7642,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A305" s="6">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A305" s="11">
         <v>45108</v>
       </c>
-      <c r="B305" s="7">
+      <c r="B305" s="11">
         <v>45169</v>
       </c>
-      <c r="C305" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D305" s="9" t="str">
+      <c r="C305" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D305" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7672,17 +7666,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A306" s="6">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A306" s="11">
         <v>45139</v>
       </c>
-      <c r="B306" s="7">
+      <c r="B306" s="11">
         <v>45201</v>
       </c>
-      <c r="C306" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D306" s="9" t="str">
+      <c r="C306" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D306" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7696,17 +7690,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A307" s="6">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A307" s="11">
         <v>45170</v>
       </c>
-      <c r="B307" s="7">
+      <c r="B307" s="11">
         <v>45233</v>
       </c>
-      <c r="C307" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D307" s="9" t="str">
+      <c r="C307" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D307" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7720,17 +7714,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A308" s="6">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A308" s="11">
         <v>45200</v>
       </c>
-      <c r="B308" s="7">
+      <c r="B308" s="11">
         <v>45260</v>
       </c>
-      <c r="C308" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D308" s="9" t="str">
+      <c r="C308" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D308" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7744,17 +7738,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A309" s="6">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A309" s="11">
         <v>45231</v>
       </c>
-      <c r="B309" s="7">
+      <c r="B309" s="11">
         <v>45300</v>
       </c>
-      <c r="C309" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D309" s="9" t="str">
+      <c r="C309" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D309" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7768,17 +7762,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A310" s="6">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A310" s="11">
         <v>45261</v>
       </c>
-      <c r="B310" s="7">
+      <c r="B310" s="11">
         <v>45323</v>
       </c>
-      <c r="C310" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D310" s="9" t="str">
+      <c r="C310" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D310" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7792,17 +7786,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A311" s="6">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A311" s="11">
         <v>45292</v>
       </c>
-      <c r="B311" s="7">
+      <c r="B311" s="11">
         <v>45352</v>
       </c>
-      <c r="C311" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D311" s="9" t="str">
+      <c r="C311" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D311" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -7816,17 +7810,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A312" s="6">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A312" s="11">
         <v>45323</v>
       </c>
-      <c r="B312" s="7">
+      <c r="B312" s="11">
         <v>45385</v>
       </c>
-      <c r="C312" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D312" s="9" t="str">
+      <c r="C312" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D312" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7840,17 +7834,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A313" s="6">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A313" s="11">
         <v>45352</v>
       </c>
-      <c r="B313" s="7">
+      <c r="B313" s="11">
         <v>45415</v>
       </c>
-      <c r="C313" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D313" s="9" t="str">
+      <c r="C313" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D313" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7864,17 +7858,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A314" s="6">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A314" s="11">
         <v>45383</v>
       </c>
-      <c r="B314" s="7">
+      <c r="B314" s="11">
         <v>45442</v>
       </c>
-      <c r="C314" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D314" s="9" t="str">
+      <c r="C314" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D314" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7888,17 +7882,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A315" s="6">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A315" s="11">
         <v>45413</v>
       </c>
-      <c r="B315" s="7">
+      <c r="B315" s="11">
         <v>45475</v>
       </c>
-      <c r="C315" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D315" s="9" t="str">
+      <c r="C315" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D315" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7912,17 +7906,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A316" s="6">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A316" s="11">
         <v>45444</v>
       </c>
-      <c r="B316" s="7">
+      <c r="B316" s="11">
         <v>45505</v>
       </c>
-      <c r="C316" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D316" s="9" t="str">
+      <c r="C316" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D316" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7936,17 +7930,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A317" s="6">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A317" s="11">
         <v>45474</v>
       </c>
-      <c r="B317" s="7">
+      <c r="B317" s="11">
         <v>45534</v>
       </c>
-      <c r="C317" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D317" s="9" t="str">
+      <c r="C317" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D317" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7960,17 +7954,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A318" s="6">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A318" s="11">
         <v>45505</v>
       </c>
-      <c r="B318" s="7">
+      <c r="B318" s="11">
         <v>45567</v>
       </c>
-      <c r="C318" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D318" s="9" t="str">
+      <c r="C318" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D318" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+2</v>
       </c>
@@ -7984,17 +7978,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A319" s="6">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A319" s="11">
         <v>45536</v>
       </c>
-      <c r="B319" s="7">
+      <c r="B319" s="11">
         <v>45596</v>
       </c>
-      <c r="C319" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D319" s="9" t="str">
+      <c r="C319" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D319" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -8008,17 +8002,17 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A320" s="6">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A320" s="11">
         <v>45566</v>
       </c>
-      <c r="B320" s="7">
+      <c r="B320" s="11">
         <v>45628</v>
       </c>
-      <c r="C320" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D320" s="9" t="str">
+      <c r="C320" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D320" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -8032,17 +8026,17 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A321" s="6">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A321" s="11">
         <v>45597</v>
       </c>
-      <c r="B321" s="7">
+      <c r="B321" s="11">
         <v>45664</v>
       </c>
-      <c r="C321" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D321" s="9" t="str">
+      <c r="C321" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D321" s="5" t="str">
         <f t="shared" si="4"/>
         <v>UTC+1</v>
       </c>
@@ -8056,18 +8050,18 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A322" s="6">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A322" s="11">
         <v>45627</v>
       </c>
-      <c r="B322" s="7">
+      <c r="B322" s="11">
         <v>45687</v>
       </c>
-      <c r="C322" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D322" s="9" t="str">
-        <f t="shared" ref="D322:D340" si="5">IF(
+      <c r="C322" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D322" s="5" t="str">
+        <f t="shared" ref="D322:D341" si="5">IF(
  AND(
   B322 &gt;= EOMONTH(DATE(YEAR(B322),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B322),3,1),0),1)
@@ -8093,17 +8087,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A323" s="6">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A323" s="11">
         <v>45658</v>
       </c>
-      <c r="B323" s="7">
+      <c r="B323" s="11">
         <v>45720</v>
       </c>
-      <c r="C323" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D323" s="9" t="str">
+      <c r="C323" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D323" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
@@ -8117,17 +8111,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A324" s="6">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A324" s="11">
         <v>45689</v>
       </c>
-      <c r="B324" s="7">
+      <c r="B324" s="11">
         <v>45748</v>
       </c>
-      <c r="C324" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D324" s="9" t="str">
+      <c r="C324" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D324" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8141,17 +8135,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A325" s="6">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A325" s="11">
         <v>45717</v>
       </c>
-      <c r="B325" s="7">
+      <c r="B325" s="11">
         <v>45779</v>
       </c>
-      <c r="C325" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D325" s="9" t="str">
+      <c r="C325" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D325" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8165,17 +8159,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A326" s="6">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A326" s="11">
         <v>45748</v>
       </c>
-      <c r="B326" s="7">
+      <c r="B326" s="11">
         <v>45811</v>
       </c>
-      <c r="C326" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D326" s="9" t="str">
+      <c r="C326" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D326" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8189,17 +8183,17 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A327" s="6">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A327" s="11">
         <v>45778</v>
       </c>
-      <c r="B327" s="7">
+      <c r="B327" s="11">
         <v>45840</v>
       </c>
-      <c r="C327" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D327" s="9" t="str">
+      <c r="C327" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D327" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8213,17 +8207,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A328" s="6">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A328" s="11">
         <v>45809</v>
       </c>
-      <c r="B328" s="7">
+      <c r="B328" s="11">
         <v>45869</v>
       </c>
-      <c r="C328" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D328" s="9" t="str">
+      <c r="C328" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D328" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8237,17 +8231,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A329" s="6">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A329" s="11">
         <v>45839</v>
       </c>
-      <c r="B329" s="7">
+      <c r="B329" s="11">
         <v>45901</v>
       </c>
-      <c r="C329" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D329" s="9" t="str">
+      <c r="C329" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D329" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8261,17 +8255,17 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A330" s="6">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A330" s="11">
         <v>45870</v>
       </c>
-      <c r="B330" s="7">
+      <c r="B330" s="11">
         <v>45932</v>
       </c>
-      <c r="C330" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D330" s="9" t="str">
+      <c r="C330" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D330" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8285,17 +8279,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A331" s="6">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A331" s="11">
         <v>45901</v>
       </c>
-      <c r="B331" s="7">
+      <c r="B331" s="11">
         <v>45960</v>
       </c>
-      <c r="C331" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D331" s="9" t="str">
+      <c r="C331" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D331" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
@@ -8309,17 +8303,17 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A332" s="6">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A332" s="11">
         <v>45931</v>
       </c>
-      <c r="B332" s="7">
+      <c r="B332" s="11">
         <v>45993</v>
       </c>
-      <c r="C332" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D332" s="9" t="str">
+      <c r="C332" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D332" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
@@ -8333,17 +8327,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A333" s="6">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A333" s="11">
         <v>45962</v>
       </c>
-      <c r="B333" s="7">
+      <c r="B333" s="11">
         <v>46030</v>
       </c>
-      <c r="C333" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D333" s="9" t="str">
+      <c r="C333" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D333" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
@@ -8357,17 +8351,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A334" s="6">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A334" s="11">
         <v>45992</v>
       </c>
-      <c r="B334" s="7">
+      <c r="B334" s="11">
         <v>46052</v>
       </c>
-      <c r="C334" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D334" s="9" t="str">
+      <c r="C334" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D334" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
@@ -8381,17 +8375,17 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A335" s="6">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A335" s="11">
         <v>46023</v>
       </c>
-      <c r="B335" s="7">
+      <c r="B335" s="11">
         <v>46085</v>
       </c>
-      <c r="C335" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D335" s="9" t="str">
+      <c r="C335" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D335" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+1</v>
       </c>
@@ -8405,17 +8399,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A336" s="6">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A336" s="11">
         <v>46054</v>
       </c>
-      <c r="B336" s="7">
+      <c r="B336" s="11">
         <v>46113</v>
       </c>
-      <c r="C336" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D336" s="9" t="str">
+      <c r="C336" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D336" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8429,17 +8423,17 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A337" s="6">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A337" s="11">
         <v>46082</v>
       </c>
-      <c r="B337" s="7">
+      <c r="B337" s="11">
         <v>46142</v>
       </c>
-      <c r="C337" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D337" s="9" t="str">
+      <c r="C337" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D337" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8453,17 +8447,17 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A338" s="6">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A338" s="11">
         <v>46113</v>
       </c>
-      <c r="B338" s="7">
+      <c r="B338" s="11">
         <v>46174</v>
       </c>
-      <c r="C338" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D338" s="9" t="str">
+      <c r="C338" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D338" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8477,17 +8471,17 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A339" s="6">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A339" s="11">
         <v>46143</v>
       </c>
-      <c r="B339" s="7">
+      <c r="B339" s="11">
         <v>46205</v>
       </c>
-      <c r="C339" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D339" s="9" t="str">
+      <c r="C339" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D339" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8501,17 +8495,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A340" s="6">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A340" s="11">
         <v>46174</v>
       </c>
-      <c r="B340" s="7">
+      <c r="B340" s="11">
         <v>46233</v>
       </c>
-      <c r="C340" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D340" s="9" t="str">
+      <c r="C340" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D340" s="5" t="str">
         <f t="shared" si="5"/>
         <v>UTC+2</v>
       </c>
@@ -8523,6 +8517,30 @@
       </c>
       <c r="G340" s="1">
         <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A341" s="11">
+        <v>46204</v>
+      </c>
+      <c r="B341" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C341" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D341" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E341" s="1">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="F341" s="1">
+        <v>6.3E-2</v>
+      </c>
+      <c r="G341" s="1">
+        <v>6.4000000000000001E-2</v>
       </c>
     </row>
   </sheetData>
